--- a/artfynd/A 11380-2026 artfynd.xlsx
+++ b/artfynd/A 11380-2026 artfynd.xlsx
@@ -6197,7 +6197,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132340992</v>
+        <v>132340989</v>
       </c>
       <c r="B54" t="n">
         <v>57948</v>
@@ -6232,10 +6232,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>435652</v>
+        <v>435579</v>
       </c>
       <c r="R54" t="n">
-        <v>7009712</v>
+        <v>7009462</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6272,7 +6272,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6299,7 +6299,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132340989</v>
+        <v>132340984</v>
       </c>
       <c r="B55" t="n">
         <v>57948</v>
@@ -6334,10 +6334,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>435579</v>
+        <v>435644</v>
       </c>
       <c r="R55" t="n">
-        <v>7009462</v>
+        <v>7009260</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6401,7 +6401,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132340984</v>
+        <v>132340992</v>
       </c>
       <c r="B56" t="n">
         <v>57948</v>
@@ -6436,10 +6436,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>435644</v>
+        <v>435652</v>
       </c>
       <c r="R56" t="n">
-        <v>7009260</v>
+        <v>7009712</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6476,7 +6476,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7531,7 +7531,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132340975</v>
+        <v>132340973</v>
       </c>
       <c r="B67" t="n">
         <v>57948</v>
@@ -7566,10 +7566,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>435422</v>
+        <v>435536</v>
       </c>
       <c r="R67" t="n">
-        <v>7009269</v>
+        <v>7009212</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7606,7 +7606,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7633,7 +7633,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132340958</v>
+        <v>132340955</v>
       </c>
       <c r="B68" t="n">
         <v>57948</v>
@@ -7668,10 +7668,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>435594</v>
+        <v>435814</v>
       </c>
       <c r="R68" t="n">
-        <v>7009012</v>
+        <v>7009258</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7708,7 +7708,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7735,7 +7735,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132340973</v>
+        <v>132340975</v>
       </c>
       <c r="B69" t="n">
         <v>57948</v>
@@ -7770,10 +7770,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>435536</v>
+        <v>435422</v>
       </c>
       <c r="R69" t="n">
-        <v>7009212</v>
+        <v>7009269</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7810,7 +7810,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7837,7 +7837,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132340955</v>
+        <v>132340958</v>
       </c>
       <c r="B70" t="n">
         <v>57948</v>
@@ -7872,10 +7872,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>435814</v>
+        <v>435594</v>
       </c>
       <c r="R70" t="n">
-        <v>7009258</v>
+        <v>7009012</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7912,7 +7912,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8245,7 +8245,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132340956</v>
+        <v>132340979</v>
       </c>
       <c r="B74" t="n">
         <v>57948</v>
@@ -8280,10 +8280,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>435811</v>
+        <v>435416</v>
       </c>
       <c r="R74" t="n">
-        <v>7009266</v>
+        <v>7009430</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8347,7 +8347,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132340979</v>
+        <v>132340956</v>
       </c>
       <c r="B75" t="n">
         <v>57948</v>
@@ -8382,10 +8382,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>435416</v>
+        <v>435811</v>
       </c>
       <c r="R75" t="n">
-        <v>7009430</v>
+        <v>7009266</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8551,10 +8551,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132340952</v>
+        <v>132341121</v>
       </c>
       <c r="B77" t="n">
-        <v>57948</v>
+        <v>91888</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8562,21 +8562,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>435863</v>
+        <v>435520</v>
       </c>
       <c r="R77" t="n">
-        <v>7009504</v>
+        <v>7009134</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8622,11 +8622,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8653,10 +8648,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132341121</v>
+        <v>132340952</v>
       </c>
       <c r="B78" t="n">
-        <v>91885</v>
+        <v>57948</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8664,21 +8659,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8688,10 +8683,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>435520</v>
+        <v>435863</v>
       </c>
       <c r="R78" t="n">
-        <v>7009134</v>
+        <v>7009504</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8724,6 +8719,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8852,7 +8852,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132340991</v>
+        <v>132340961</v>
       </c>
       <c r="B80" t="n">
         <v>57948</v>
@@ -8887,10 +8887,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>435608</v>
+        <v>435531</v>
       </c>
       <c r="R80" t="n">
-        <v>7009554</v>
+        <v>7009066</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8927,7 +8927,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8954,7 +8954,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132340976</v>
+        <v>132340991</v>
       </c>
       <c r="B81" t="n">
         <v>57948</v>
@@ -8989,10 +8989,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>435445</v>
+        <v>435608</v>
       </c>
       <c r="R81" t="n">
-        <v>7009286</v>
+        <v>7009554</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9056,7 +9056,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132340961</v>
+        <v>132340976</v>
       </c>
       <c r="B82" t="n">
         <v>57948</v>
@@ -9091,10 +9091,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>435531</v>
+        <v>435445</v>
       </c>
       <c r="R82" t="n">
-        <v>7009066</v>
+        <v>7009286</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9161,7 +9161,7 @@
         <v>132341120</v>
       </c>
       <c r="B83" t="n">
-        <v>91885</v>
+        <v>91888</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 11380-2026 artfynd.xlsx
+++ b/artfynd/A 11380-2026 artfynd.xlsx
@@ -6197,7 +6197,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132340989</v>
+        <v>132340984</v>
       </c>
       <c r="B54" t="n">
         <v>57948</v>
@@ -6232,10 +6232,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>435579</v>
+        <v>435644</v>
       </c>
       <c r="R54" t="n">
-        <v>7009462</v>
+        <v>7009260</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6299,7 +6299,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132340984</v>
+        <v>132340989</v>
       </c>
       <c r="B55" t="n">
         <v>57948</v>
@@ -6334,10 +6334,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>435644</v>
+        <v>435579</v>
       </c>
       <c r="R55" t="n">
-        <v>7009260</v>
+        <v>7009462</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -9158,10 +9158,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132341120</v>
+        <v>132340978</v>
       </c>
       <c r="B83" t="n">
-        <v>91888</v>
+        <v>57948</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9169,21 +9169,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9193,10 +9193,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>435875</v>
+        <v>435358</v>
       </c>
       <c r="R83" t="n">
-        <v>7009285</v>
+        <v>7009404</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9229,6 +9229,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9255,7 +9260,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132340978</v>
+        <v>132340951</v>
       </c>
       <c r="B84" t="n">
         <v>57948</v>
@@ -9290,10 +9295,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>435358</v>
+        <v>435770</v>
       </c>
       <c r="R84" t="n">
-        <v>7009404</v>
+        <v>7009576</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9357,10 +9362,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132340951</v>
+        <v>132341120</v>
       </c>
       <c r="B85" t="n">
-        <v>57948</v>
+        <v>91888</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9368,21 +9373,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9392,10 +9397,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>435770</v>
+        <v>435875</v>
       </c>
       <c r="R85" t="n">
-        <v>7009576</v>
+        <v>7009285</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9428,11 +9433,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD85" t="b">

--- a/artfynd/A 11380-2026 artfynd.xlsx
+++ b/artfynd/A 11380-2026 artfynd.xlsx
@@ -6197,7 +6197,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132340984</v>
+        <v>132340989</v>
       </c>
       <c r="B54" t="n">
         <v>57948</v>
@@ -6232,10 +6232,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>435644</v>
+        <v>435579</v>
       </c>
       <c r="R54" t="n">
-        <v>7009260</v>
+        <v>7009462</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6299,7 +6299,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132340989</v>
+        <v>132340984</v>
       </c>
       <c r="B55" t="n">
         <v>57948</v>
@@ -6334,10 +6334,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>435579</v>
+        <v>435644</v>
       </c>
       <c r="R55" t="n">
-        <v>7009462</v>
+        <v>7009260</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>

--- a/artfynd/A 11380-2026 artfynd.xlsx
+++ b/artfynd/A 11380-2026 artfynd.xlsx
@@ -7531,7 +7531,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132340973</v>
+        <v>132340955</v>
       </c>
       <c r="B67" t="n">
         <v>57948</v>
@@ -7566,10 +7566,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>435536</v>
+        <v>435814</v>
       </c>
       <c r="R67" t="n">
-        <v>7009212</v>
+        <v>7009258</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7606,7 +7606,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7633,7 +7633,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132340955</v>
+        <v>132340975</v>
       </c>
       <c r="B68" t="n">
         <v>57948</v>
@@ -7668,10 +7668,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>435814</v>
+        <v>435422</v>
       </c>
       <c r="R68" t="n">
-        <v>7009258</v>
+        <v>7009269</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7708,7 +7708,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7735,7 +7735,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132340975</v>
+        <v>132340958</v>
       </c>
       <c r="B69" t="n">
         <v>57948</v>
@@ -7770,10 +7770,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>435422</v>
+        <v>435594</v>
       </c>
       <c r="R69" t="n">
-        <v>7009269</v>
+        <v>7009012</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7837,7 +7837,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132340958</v>
+        <v>132340973</v>
       </c>
       <c r="B70" t="n">
         <v>57948</v>
@@ -7872,10 +7872,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>435594</v>
+        <v>435536</v>
       </c>
       <c r="R70" t="n">
-        <v>7009012</v>
+        <v>7009212</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7912,7 +7912,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8551,10 +8551,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132341121</v>
+        <v>132340952</v>
       </c>
       <c r="B77" t="n">
-        <v>91888</v>
+        <v>57948</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8562,21 +8562,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>435520</v>
+        <v>435863</v>
       </c>
       <c r="R77" t="n">
-        <v>7009134</v>
+        <v>7009504</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8622,6 +8622,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8648,10 +8653,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132340952</v>
+        <v>132341121</v>
       </c>
       <c r="B78" t="n">
-        <v>57948</v>
+        <v>91888</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8659,21 +8664,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8683,10 +8688,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>435863</v>
+        <v>435520</v>
       </c>
       <c r="R78" t="n">
-        <v>7009504</v>
+        <v>7009134</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8719,11 +8724,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">

--- a/artfynd/A 11380-2026 artfynd.xlsx
+++ b/artfynd/A 11380-2026 artfynd.xlsx
@@ -9158,10 +9158,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132340978</v>
+        <v>132341120</v>
       </c>
       <c r="B83" t="n">
-        <v>57948</v>
+        <v>91888</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9169,21 +9169,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9193,10 +9193,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>435358</v>
+        <v>435875</v>
       </c>
       <c r="R83" t="n">
-        <v>7009404</v>
+        <v>7009285</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9229,11 +9229,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9260,7 +9255,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132340951</v>
+        <v>132340978</v>
       </c>
       <c r="B84" t="n">
         <v>57948</v>
@@ -9295,10 +9290,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>435770</v>
+        <v>435358</v>
       </c>
       <c r="R84" t="n">
-        <v>7009576</v>
+        <v>7009404</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9362,10 +9357,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132341120</v>
+        <v>132340951</v>
       </c>
       <c r="B85" t="n">
-        <v>91888</v>
+        <v>57948</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9373,21 +9368,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9397,10 +9392,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>435875</v>
+        <v>435770</v>
       </c>
       <c r="R85" t="n">
-        <v>7009285</v>
+        <v>7009576</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9433,6 +9428,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD85" t="b">

--- a/artfynd/A 11380-2026 artfynd.xlsx
+++ b/artfynd/A 11380-2026 artfynd.xlsx
@@ -7531,7 +7531,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132340955</v>
+        <v>132340973</v>
       </c>
       <c r="B67" t="n">
         <v>57948</v>
@@ -7566,10 +7566,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>435814</v>
+        <v>435536</v>
       </c>
       <c r="R67" t="n">
-        <v>7009258</v>
+        <v>7009212</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7606,7 +7606,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7633,7 +7633,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132340975</v>
+        <v>132340955</v>
       </c>
       <c r="B68" t="n">
         <v>57948</v>
@@ -7668,10 +7668,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>435422</v>
+        <v>435814</v>
       </c>
       <c r="R68" t="n">
-        <v>7009269</v>
+        <v>7009258</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7708,7 +7708,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7735,7 +7735,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132340958</v>
+        <v>132340975</v>
       </c>
       <c r="B69" t="n">
         <v>57948</v>
@@ -7770,10 +7770,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>435594</v>
+        <v>435422</v>
       </c>
       <c r="R69" t="n">
-        <v>7009012</v>
+        <v>7009269</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7837,7 +7837,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132340973</v>
+        <v>132340958</v>
       </c>
       <c r="B70" t="n">
         <v>57948</v>
@@ -7872,10 +7872,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>435536</v>
+        <v>435594</v>
       </c>
       <c r="R70" t="n">
-        <v>7009212</v>
+        <v>7009012</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7912,7 +7912,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9158,10 +9158,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132341120</v>
+        <v>132340978</v>
       </c>
       <c r="B83" t="n">
-        <v>91888</v>
+        <v>57948</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9169,21 +9169,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9193,10 +9193,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>435875</v>
+        <v>435358</v>
       </c>
       <c r="R83" t="n">
-        <v>7009285</v>
+        <v>7009404</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9229,6 +9229,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9255,7 +9260,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132340978</v>
+        <v>132340951</v>
       </c>
       <c r="B84" t="n">
         <v>57948</v>
@@ -9290,10 +9295,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>435358</v>
+        <v>435770</v>
       </c>
       <c r="R84" t="n">
-        <v>7009404</v>
+        <v>7009576</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9357,10 +9362,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132340951</v>
+        <v>132341120</v>
       </c>
       <c r="B85" t="n">
-        <v>57948</v>
+        <v>91888</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9368,21 +9373,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9392,10 +9397,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>435770</v>
+        <v>435875</v>
       </c>
       <c r="R85" t="n">
-        <v>7009576</v>
+        <v>7009285</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9428,11 +9433,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD85" t="b">

--- a/artfynd/A 11380-2026 artfynd.xlsx
+++ b/artfynd/A 11380-2026 artfynd.xlsx
@@ -4764,7 +4764,7 @@
         <v>132340980</v>
       </c>
       <c r="B40" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4863,10 +4863,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132340957</v>
+        <v>132340953</v>
       </c>
       <c r="B41" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4898,10 +4898,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>435678</v>
+        <v>435992</v>
       </c>
       <c r="R41" t="n">
-        <v>7009061</v>
+        <v>7009388</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4938,7 +4938,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4968,7 +4968,7 @@
         <v>132340964</v>
       </c>
       <c r="B42" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5075,10 +5075,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132340953</v>
+        <v>132340957</v>
       </c>
       <c r="B43" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5110,10 +5110,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>435992</v>
+        <v>435678</v>
       </c>
       <c r="R43" t="n">
-        <v>7009388</v>
+        <v>7009061</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5150,7 +5150,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5177,10 +5177,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132340996</v>
+        <v>132340986</v>
       </c>
       <c r="B44" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5212,10 +5212,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>435657</v>
+        <v>435632</v>
       </c>
       <c r="R44" t="n">
-        <v>7009715</v>
+        <v>7009284</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5252,7 +5252,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5279,10 +5279,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132340977</v>
+        <v>132340996</v>
       </c>
       <c r="B45" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5314,10 +5314,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>435438</v>
+        <v>435657</v>
       </c>
       <c r="R45" t="n">
-        <v>7009287</v>
+        <v>7009715</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5381,10 +5381,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132340986</v>
+        <v>132340977</v>
       </c>
       <c r="B46" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5416,10 +5416,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>435632</v>
+        <v>435438</v>
       </c>
       <c r="R46" t="n">
-        <v>7009284</v>
+        <v>7009287</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5483,10 +5483,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132340997</v>
+        <v>132340983</v>
       </c>
       <c r="B47" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5518,10 +5518,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>435714</v>
+        <v>435570</v>
       </c>
       <c r="R47" t="n">
-        <v>7009769</v>
+        <v>7009342</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5558,7 +5558,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5585,10 +5585,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132340983</v>
+        <v>132340997</v>
       </c>
       <c r="B48" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5620,10 +5620,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>435570</v>
+        <v>435714</v>
       </c>
       <c r="R48" t="n">
-        <v>7009342</v>
+        <v>7009769</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5660,7 +5660,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5690,7 +5690,7 @@
         <v>132340974</v>
       </c>
       <c r="B49" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5792,7 +5792,7 @@
         <v>132340962</v>
       </c>
       <c r="B50" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         <v>132340970</v>
       </c>
       <c r="B51" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5996,7 +5996,7 @@
         <v>132340995</v>
       </c>
       <c r="B52" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>132340971</v>
       </c>
       <c r="B53" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6197,10 +6197,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132340989</v>
+        <v>132340984</v>
       </c>
       <c r="B54" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6232,10 +6232,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>435579</v>
+        <v>435644</v>
       </c>
       <c r="R54" t="n">
-        <v>7009462</v>
+        <v>7009260</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6299,10 +6299,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132340984</v>
+        <v>132340982</v>
       </c>
       <c r="B55" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6334,10 +6334,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>435644</v>
+        <v>435574</v>
       </c>
       <c r="R55" t="n">
-        <v>7009260</v>
+        <v>7009351</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6374,7 +6374,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6404,7 +6404,7 @@
         <v>132340992</v>
       </c>
       <c r="B56" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6503,10 +6503,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132340982</v>
+        <v>132340989</v>
       </c>
       <c r="B57" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6538,10 +6538,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>435574</v>
+        <v>435579</v>
       </c>
       <c r="R57" t="n">
-        <v>7009351</v>
+        <v>7009462</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6605,10 +6605,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132340967</v>
+        <v>132340968</v>
       </c>
       <c r="B58" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6640,10 +6640,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>435511</v>
+        <v>435492</v>
       </c>
       <c r="R58" t="n">
-        <v>7009171</v>
+        <v>7009187</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6707,10 +6707,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132340985</v>
+        <v>132340967</v>
       </c>
       <c r="B59" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6736,24 +6736,16 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>435645</v>
+        <v>435511</v>
       </c>
       <c r="R59" t="n">
-        <v>7009273</v>
+        <v>7009171</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6790,7 +6782,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Bohål ca 1,8 m upp i grantickerötad granhögstubbe.Öppning ca 4,5cm i diameter.Ganska färskt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6817,10 +6809,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132340968</v>
+        <v>132340985</v>
       </c>
       <c r="B60" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6846,16 +6838,24 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>435492</v>
+        <v>435645</v>
       </c>
       <c r="R60" t="n">
-        <v>7009187</v>
+        <v>7009273</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6892,7 +6892,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Bohål ca 1,8 m upp i grantickerötad granhögstubbe.Öppning ca 4,5cm i diameter.Ganska färskt</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6919,10 +6919,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132340990</v>
+        <v>132340988</v>
       </c>
       <c r="B61" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6954,10 +6954,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>435589</v>
+        <v>435597</v>
       </c>
       <c r="R61" t="n">
-        <v>7009520</v>
+        <v>7009455</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7021,10 +7021,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132340988</v>
+        <v>132340965</v>
       </c>
       <c r="B62" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7056,10 +7056,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>435597</v>
+        <v>435503</v>
       </c>
       <c r="R62" t="n">
-        <v>7009455</v>
+        <v>7009162</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7123,10 +7123,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132340965</v>
+        <v>132340990</v>
       </c>
       <c r="B63" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7158,10 +7158,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>435503</v>
+        <v>435589</v>
       </c>
       <c r="R63" t="n">
-        <v>7009162</v>
+        <v>7009520</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7228,7 +7228,7 @@
         <v>132340963</v>
       </c>
       <c r="B64" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         <v>132340972</v>
       </c>
       <c r="B65" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7432,7 +7432,7 @@
         <v>132340960</v>
       </c>
       <c r="B66" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7531,10 +7531,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132340973</v>
+        <v>132340958</v>
       </c>
       <c r="B67" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7566,10 +7566,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>435536</v>
+        <v>435594</v>
       </c>
       <c r="R67" t="n">
-        <v>7009212</v>
+        <v>7009012</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7606,7 +7606,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7633,10 +7633,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132340955</v>
+        <v>132340975</v>
       </c>
       <c r="B68" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7668,10 +7668,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>435814</v>
+        <v>435422</v>
       </c>
       <c r="R68" t="n">
-        <v>7009258</v>
+        <v>7009269</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7708,7 +7708,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7735,10 +7735,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132340975</v>
+        <v>132340955</v>
       </c>
       <c r="B69" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7770,10 +7770,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>435422</v>
+        <v>435814</v>
       </c>
       <c r="R69" t="n">
-        <v>7009269</v>
+        <v>7009258</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7810,7 +7810,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7837,10 +7837,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132340958</v>
+        <v>132340973</v>
       </c>
       <c r="B70" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7872,10 +7872,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>435594</v>
+        <v>435536</v>
       </c>
       <c r="R70" t="n">
-        <v>7009012</v>
+        <v>7009212</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7912,7 +7912,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7939,10 +7939,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132340998</v>
+        <v>132340994</v>
       </c>
       <c r="B71" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7974,10 +7974,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>435702</v>
+        <v>435648</v>
       </c>
       <c r="R71" t="n">
-        <v>7009759</v>
+        <v>7009710</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8041,10 +8041,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132340994</v>
+        <v>132340998</v>
       </c>
       <c r="B72" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8076,10 +8076,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>435648</v>
+        <v>435702</v>
       </c>
       <c r="R72" t="n">
-        <v>7009710</v>
+        <v>7009759</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8146,7 +8146,7 @@
         <v>132340966</v>
       </c>
       <c r="B73" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8245,10 +8245,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132340979</v>
+        <v>132340956</v>
       </c>
       <c r="B74" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8280,10 +8280,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>435416</v>
+        <v>435811</v>
       </c>
       <c r="R74" t="n">
-        <v>7009430</v>
+        <v>7009266</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8347,10 +8347,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132340956</v>
+        <v>132340979</v>
       </c>
       <c r="B75" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8382,10 +8382,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>435811</v>
+        <v>435416</v>
       </c>
       <c r="R75" t="n">
-        <v>7009266</v>
+        <v>7009430</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8452,7 +8452,7 @@
         <v>132340954</v>
       </c>
       <c r="B76" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8551,10 +8551,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132340952</v>
+        <v>132341121</v>
       </c>
       <c r="B77" t="n">
-        <v>57948</v>
+        <v>91894</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8562,21 +8562,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>435863</v>
+        <v>435520</v>
       </c>
       <c r="R77" t="n">
-        <v>7009504</v>
+        <v>7009134</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8622,11 +8622,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8653,10 +8648,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132341121</v>
+        <v>132340952</v>
       </c>
       <c r="B78" t="n">
-        <v>91888</v>
+        <v>57949</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8664,21 +8659,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8688,10 +8683,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>435520</v>
+        <v>435863</v>
       </c>
       <c r="R78" t="n">
-        <v>7009134</v>
+        <v>7009504</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8724,6 +8719,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8750,10 +8750,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132340987</v>
+        <v>132340976</v>
       </c>
       <c r="B79" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8785,10 +8785,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>435703</v>
+        <v>435445</v>
       </c>
       <c r="R79" t="n">
-        <v>7009319</v>
+        <v>7009286</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8825,7 +8825,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8855,7 +8855,7 @@
         <v>132340961</v>
       </c>
       <c r="B80" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8954,10 +8954,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132340991</v>
+        <v>132340987</v>
       </c>
       <c r="B81" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8989,10 +8989,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>435608</v>
+        <v>435703</v>
       </c>
       <c r="R81" t="n">
-        <v>7009554</v>
+        <v>7009319</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9056,10 +9056,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132340976</v>
+        <v>132340991</v>
       </c>
       <c r="B82" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9091,10 +9091,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>435445</v>
+        <v>435608</v>
       </c>
       <c r="R82" t="n">
-        <v>7009286</v>
+        <v>7009554</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9131,7 +9131,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9158,10 +9158,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132340978</v>
+        <v>132341120</v>
       </c>
       <c r="B83" t="n">
-        <v>57948</v>
+        <v>91894</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9169,21 +9169,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9193,10 +9193,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>435358</v>
+        <v>435875</v>
       </c>
       <c r="R83" t="n">
-        <v>7009404</v>
+        <v>7009285</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9229,11 +9229,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9260,10 +9255,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132340951</v>
+        <v>132340978</v>
       </c>
       <c r="B84" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9295,10 +9290,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>435770</v>
+        <v>435358</v>
       </c>
       <c r="R84" t="n">
-        <v>7009576</v>
+        <v>7009404</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9362,10 +9357,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132341120</v>
+        <v>132340951</v>
       </c>
       <c r="B85" t="n">
-        <v>91888</v>
+        <v>57949</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9373,21 +9368,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9397,10 +9392,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>435875</v>
+        <v>435770</v>
       </c>
       <c r="R85" t="n">
-        <v>7009285</v>
+        <v>7009576</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9433,6 +9428,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9462,7 +9462,7 @@
         <v>132340969</v>
       </c>
       <c r="B86" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9564,7 +9564,7 @@
         <v>132340959</v>
       </c>
       <c r="B87" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 11380-2026 artfynd.xlsx
+++ b/artfynd/A 11380-2026 artfynd.xlsx
@@ -4761,10 +4761,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132340980</v>
+        <v>132340964</v>
       </c>
       <c r="B40" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4790,16 +4790,24 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>435430</v>
+        <v>435539</v>
       </c>
       <c r="R40" t="n">
-        <v>7009465</v>
+        <v>7009104</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4836,7 +4844,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Bohål ca 1,7m upp i grantickerötad granhögstubbe</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4863,10 +4871,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132340953</v>
+        <v>132340980</v>
       </c>
       <c r="B41" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4898,10 +4906,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>435992</v>
+        <v>435430</v>
       </c>
       <c r="R41" t="n">
-        <v>7009388</v>
+        <v>7009465</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4965,10 +4973,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132340964</v>
+        <v>132340957</v>
       </c>
       <c r="B42" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4994,24 +5002,16 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>435539</v>
+        <v>435678</v>
       </c>
       <c r="R42" t="n">
-        <v>7009104</v>
+        <v>7009061</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Bohål ca 1,7m upp i grantickerötad granhögstubbe</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5075,10 +5075,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132340957</v>
+        <v>132340953</v>
       </c>
       <c r="B43" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5110,10 +5110,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>435678</v>
+        <v>435992</v>
       </c>
       <c r="R43" t="n">
-        <v>7009061</v>
+        <v>7009388</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5150,7 +5150,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5177,10 +5177,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132340986</v>
+        <v>132340996</v>
       </c>
       <c r="B44" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5212,10 +5212,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>435632</v>
+        <v>435657</v>
       </c>
       <c r="R44" t="n">
-        <v>7009284</v>
+        <v>7009715</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5252,7 +5252,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5279,10 +5279,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132340996</v>
+        <v>132340977</v>
       </c>
       <c r="B45" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5314,10 +5314,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>435657</v>
+        <v>435438</v>
       </c>
       <c r="R45" t="n">
-        <v>7009715</v>
+        <v>7009287</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5381,10 +5381,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132340977</v>
+        <v>132340986</v>
       </c>
       <c r="B46" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5416,10 +5416,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>435438</v>
+        <v>435632</v>
       </c>
       <c r="R46" t="n">
-        <v>7009287</v>
+        <v>7009284</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5483,10 +5483,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132340983</v>
+        <v>132340997</v>
       </c>
       <c r="B47" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5518,10 +5518,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>435570</v>
+        <v>435714</v>
       </c>
       <c r="R47" t="n">
-        <v>7009342</v>
+        <v>7009769</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5558,7 +5558,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5585,10 +5585,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132340997</v>
+        <v>132340983</v>
       </c>
       <c r="B48" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5620,10 +5620,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>435714</v>
+        <v>435570</v>
       </c>
       <c r="R48" t="n">
-        <v>7009769</v>
+        <v>7009342</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5660,7 +5660,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5690,7 +5690,7 @@
         <v>132340974</v>
       </c>
       <c r="B49" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5792,7 +5792,7 @@
         <v>132340962</v>
       </c>
       <c r="B50" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5891,10 +5891,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132340970</v>
+        <v>132340995</v>
       </c>
       <c r="B51" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5926,10 +5926,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>435522</v>
+        <v>435651</v>
       </c>
       <c r="R51" t="n">
-        <v>7009195</v>
+        <v>7009715</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5966,7 +5966,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5993,10 +5993,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132340995</v>
+        <v>132340970</v>
       </c>
       <c r="B52" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>435651</v>
+        <v>435522</v>
       </c>
       <c r="R52" t="n">
-        <v>7009715</v>
+        <v>7009195</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6068,7 +6068,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6098,7 +6098,7 @@
         <v>132340971</v>
       </c>
       <c r="B53" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6197,10 +6197,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132340984</v>
+        <v>132340989</v>
       </c>
       <c r="B54" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6232,10 +6232,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>435644</v>
+        <v>435579</v>
       </c>
       <c r="R54" t="n">
-        <v>7009260</v>
+        <v>7009462</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6299,10 +6299,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132340982</v>
+        <v>132340984</v>
       </c>
       <c r="B55" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6334,10 +6334,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>435574</v>
+        <v>435644</v>
       </c>
       <c r="R55" t="n">
-        <v>7009351</v>
+        <v>7009260</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6374,7 +6374,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6404,7 +6404,7 @@
         <v>132340992</v>
       </c>
       <c r="B56" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6503,10 +6503,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132340989</v>
+        <v>132340982</v>
       </c>
       <c r="B57" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6538,10 +6538,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>435579</v>
+        <v>435574</v>
       </c>
       <c r="R57" t="n">
-        <v>7009462</v>
+        <v>7009351</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6605,10 +6605,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132340968</v>
+        <v>132340985</v>
       </c>
       <c r="B58" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6634,16 +6634,24 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>435492</v>
+        <v>435645</v>
       </c>
       <c r="R58" t="n">
-        <v>7009187</v>
+        <v>7009273</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6680,7 +6688,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Bohål ca 1,8 m upp i grantickerötad granhögstubbe.Öppning ca 4,5cm i diameter.Ganska färskt</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6707,10 +6715,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132340967</v>
+        <v>132340968</v>
       </c>
       <c r="B59" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6742,10 +6750,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>435511</v>
+        <v>435492</v>
       </c>
       <c r="R59" t="n">
-        <v>7009171</v>
+        <v>7009187</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6809,10 +6817,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132340985</v>
+        <v>132340967</v>
       </c>
       <c r="B60" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6838,24 +6846,16 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>435645</v>
+        <v>435511</v>
       </c>
       <c r="R60" t="n">
-        <v>7009273</v>
+        <v>7009171</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6892,7 +6892,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Bohål ca 1,8 m upp i grantickerötad granhögstubbe.Öppning ca 4,5cm i diameter.Ganska färskt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6919,10 +6919,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132340988</v>
+        <v>132340990</v>
       </c>
       <c r="B61" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6954,10 +6954,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>435597</v>
+        <v>435589</v>
       </c>
       <c r="R61" t="n">
-        <v>7009455</v>
+        <v>7009520</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7024,7 +7024,7 @@
         <v>132340965</v>
       </c>
       <c r="B62" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7123,10 +7123,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132340990</v>
+        <v>132340988</v>
       </c>
       <c r="B63" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7158,10 +7158,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>435589</v>
+        <v>435597</v>
       </c>
       <c r="R63" t="n">
-        <v>7009520</v>
+        <v>7009455</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7228,7 +7228,7 @@
         <v>132340963</v>
       </c>
       <c r="B64" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         <v>132340972</v>
       </c>
       <c r="B65" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7432,7 +7432,7 @@
         <v>132340960</v>
       </c>
       <c r="B66" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7531,10 +7531,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132340958</v>
+        <v>132340975</v>
       </c>
       <c r="B67" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7566,10 +7566,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>435594</v>
+        <v>435422</v>
       </c>
       <c r="R67" t="n">
-        <v>7009012</v>
+        <v>7009269</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7633,10 +7633,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132340975</v>
+        <v>132340973</v>
       </c>
       <c r="B68" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7668,10 +7668,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>435422</v>
+        <v>435536</v>
       </c>
       <c r="R68" t="n">
-        <v>7009269</v>
+        <v>7009212</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7708,7 +7708,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7738,7 +7738,7 @@
         <v>132340955</v>
       </c>
       <c r="B69" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7837,10 +7837,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132340973</v>
+        <v>132340958</v>
       </c>
       <c r="B70" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7872,10 +7872,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>435536</v>
+        <v>435594</v>
       </c>
       <c r="R70" t="n">
-        <v>7009212</v>
+        <v>7009012</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7912,7 +7912,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7942,7 +7942,7 @@
         <v>132340994</v>
       </c>
       <c r="B71" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8041,10 +8041,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132340998</v>
+        <v>132340966</v>
       </c>
       <c r="B72" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8076,10 +8076,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>435702</v>
+        <v>435505</v>
       </c>
       <c r="R72" t="n">
-        <v>7009759</v>
+        <v>7009166</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8116,7 +8116,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8143,10 +8143,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132340966</v>
+        <v>132340998</v>
       </c>
       <c r="B73" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8178,10 +8178,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>435505</v>
+        <v>435702</v>
       </c>
       <c r="R73" t="n">
-        <v>7009166</v>
+        <v>7009759</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8218,7 +8218,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8245,10 +8245,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132340956</v>
+        <v>132340979</v>
       </c>
       <c r="B74" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8280,10 +8280,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>435811</v>
+        <v>435416</v>
       </c>
       <c r="R74" t="n">
-        <v>7009266</v>
+        <v>7009430</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8347,10 +8347,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132340979</v>
+        <v>132340956</v>
       </c>
       <c r="B75" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8382,10 +8382,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>435416</v>
+        <v>435811</v>
       </c>
       <c r="R75" t="n">
-        <v>7009430</v>
+        <v>7009266</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8452,7 +8452,7 @@
         <v>132340954</v>
       </c>
       <c r="B76" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8554,7 +8554,7 @@
         <v>132341121</v>
       </c>
       <c r="B77" t="n">
-        <v>91894</v>
+        <v>91904</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8651,7 +8651,7 @@
         <v>132340952</v>
       </c>
       <c r="B78" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8750,10 +8750,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132340976</v>
+        <v>132340961</v>
       </c>
       <c r="B79" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8785,10 +8785,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>435445</v>
+        <v>435531</v>
       </c>
       <c r="R79" t="n">
-        <v>7009286</v>
+        <v>7009066</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8852,10 +8852,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132340961</v>
+        <v>132340991</v>
       </c>
       <c r="B80" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8887,10 +8887,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>435531</v>
+        <v>435608</v>
       </c>
       <c r="R80" t="n">
-        <v>7009066</v>
+        <v>7009554</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8927,7 +8927,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8957,7 +8957,7 @@
         <v>132340987</v>
       </c>
       <c r="B81" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9056,10 +9056,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132340991</v>
+        <v>132340976</v>
       </c>
       <c r="B82" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9091,10 +9091,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>435608</v>
+        <v>435445</v>
       </c>
       <c r="R82" t="n">
-        <v>7009554</v>
+        <v>7009286</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9131,7 +9131,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9161,7 +9161,7 @@
         <v>132341120</v>
       </c>
       <c r="B83" t="n">
-        <v>91894</v>
+        <v>91904</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9255,10 +9255,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132340978</v>
+        <v>132340951</v>
       </c>
       <c r="B84" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9290,10 +9290,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>435358</v>
+        <v>435770</v>
       </c>
       <c r="R84" t="n">
-        <v>7009404</v>
+        <v>7009576</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9357,10 +9357,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132340951</v>
+        <v>132340978</v>
       </c>
       <c r="B85" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9392,10 +9392,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>435770</v>
+        <v>435358</v>
       </c>
       <c r="R85" t="n">
-        <v>7009576</v>
+        <v>7009404</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9459,10 +9459,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132340969</v>
+        <v>132340959</v>
       </c>
       <c r="B86" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9494,10 +9494,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>435503</v>
+        <v>435523</v>
       </c>
       <c r="R86" t="n">
-        <v>7009197</v>
+        <v>7009035</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9561,10 +9561,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132340959</v>
+        <v>132340969</v>
       </c>
       <c r="B87" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9596,10 +9596,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>435523</v>
+        <v>435503</v>
       </c>
       <c r="R87" t="n">
-        <v>7009035</v>
+        <v>7009197</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9636,7 +9636,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">

--- a/artfynd/A 11380-2026 artfynd.xlsx
+++ b/artfynd/A 11380-2026 artfynd.xlsx
@@ -4761,7 +4761,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132340964</v>
+        <v>132340980</v>
       </c>
       <c r="B40" t="n">
         <v>57953</v>
@@ -4790,24 +4790,16 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>435539</v>
+        <v>435430</v>
       </c>
       <c r="R40" t="n">
-        <v>7009104</v>
+        <v>7009465</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4844,7 +4836,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Bohål ca 1,7m upp i grantickerötad granhögstubbe</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4871,7 +4863,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132340980</v>
+        <v>132340953</v>
       </c>
       <c r="B41" t="n">
         <v>57953</v>
@@ -4906,10 +4898,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>435430</v>
+        <v>435992</v>
       </c>
       <c r="R41" t="n">
-        <v>7009465</v>
+        <v>7009388</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4973,7 +4965,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132340957</v>
+        <v>132340964</v>
       </c>
       <c r="B42" t="n">
         <v>57953</v>
@@ -5002,16 +4994,24 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>435678</v>
+        <v>435539</v>
       </c>
       <c r="R42" t="n">
-        <v>7009061</v>
+        <v>7009104</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Bohål ca 1,7m upp i grantickerötad granhögstubbe</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5075,7 +5075,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132340953</v>
+        <v>132340957</v>
       </c>
       <c r="B43" t="n">
         <v>57953</v>
@@ -5110,10 +5110,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>435992</v>
+        <v>435678</v>
       </c>
       <c r="R43" t="n">
-        <v>7009388</v>
+        <v>7009061</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5150,7 +5150,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5177,7 +5177,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132340996</v>
+        <v>132340986</v>
       </c>
       <c r="B44" t="n">
         <v>57953</v>
@@ -5212,10 +5212,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>435657</v>
+        <v>435632</v>
       </c>
       <c r="R44" t="n">
-        <v>7009715</v>
+        <v>7009284</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5252,7 +5252,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5279,7 +5279,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132340977</v>
+        <v>132340996</v>
       </c>
       <c r="B45" t="n">
         <v>57953</v>
@@ -5314,10 +5314,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>435438</v>
+        <v>435657</v>
       </c>
       <c r="R45" t="n">
-        <v>7009287</v>
+        <v>7009715</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5381,7 +5381,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132340986</v>
+        <v>132340977</v>
       </c>
       <c r="B46" t="n">
         <v>57953</v>
@@ -5416,10 +5416,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>435632</v>
+        <v>435438</v>
       </c>
       <c r="R46" t="n">
-        <v>7009284</v>
+        <v>7009287</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5483,7 +5483,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132340997</v>
+        <v>132340983</v>
       </c>
       <c r="B47" t="n">
         <v>57953</v>
@@ -5518,10 +5518,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>435714</v>
+        <v>435570</v>
       </c>
       <c r="R47" t="n">
-        <v>7009769</v>
+        <v>7009342</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5558,7 +5558,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5585,7 +5585,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132340983</v>
+        <v>132340997</v>
       </c>
       <c r="B48" t="n">
         <v>57953</v>
@@ -5620,10 +5620,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>435570</v>
+        <v>435714</v>
       </c>
       <c r="R48" t="n">
-        <v>7009342</v>
+        <v>7009769</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5660,7 +5660,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5891,7 +5891,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132340995</v>
+        <v>132340970</v>
       </c>
       <c r="B51" t="n">
         <v>57953</v>
@@ -5926,10 +5926,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>435651</v>
+        <v>435522</v>
       </c>
       <c r="R51" t="n">
-        <v>7009715</v>
+        <v>7009195</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5966,7 +5966,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5993,7 +5993,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132340970</v>
+        <v>132340995</v>
       </c>
       <c r="B52" t="n">
         <v>57953</v>
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>435522</v>
+        <v>435651</v>
       </c>
       <c r="R52" t="n">
-        <v>7009195</v>
+        <v>7009715</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6068,7 +6068,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6197,7 +6197,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132340989</v>
+        <v>132340984</v>
       </c>
       <c r="B54" t="n">
         <v>57953</v>
@@ -6232,10 +6232,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>435579</v>
+        <v>435644</v>
       </c>
       <c r="R54" t="n">
-        <v>7009462</v>
+        <v>7009260</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6299,7 +6299,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132340984</v>
+        <v>132340982</v>
       </c>
       <c r="B55" t="n">
         <v>57953</v>
@@ -6334,10 +6334,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>435644</v>
+        <v>435574</v>
       </c>
       <c r="R55" t="n">
-        <v>7009260</v>
+        <v>7009351</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6374,7 +6374,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6503,7 +6503,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132340982</v>
+        <v>132340989</v>
       </c>
       <c r="B57" t="n">
         <v>57953</v>
@@ -6538,10 +6538,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>435574</v>
+        <v>435579</v>
       </c>
       <c r="R57" t="n">
-        <v>7009351</v>
+        <v>7009462</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6605,7 +6605,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132340985</v>
+        <v>132340968</v>
       </c>
       <c r="B58" t="n">
         <v>57953</v>
@@ -6634,24 +6634,16 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>435645</v>
+        <v>435492</v>
       </c>
       <c r="R58" t="n">
-        <v>7009273</v>
+        <v>7009187</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6688,7 +6680,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Bohål ca 1,8 m upp i grantickerötad granhögstubbe.Öppning ca 4,5cm i diameter.Ganska färskt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6715,7 +6707,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132340968</v>
+        <v>132340967</v>
       </c>
       <c r="B59" t="n">
         <v>57953</v>
@@ -6750,10 +6742,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>435492</v>
+        <v>435511</v>
       </c>
       <c r="R59" t="n">
-        <v>7009187</v>
+        <v>7009171</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6817,7 +6809,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132340967</v>
+        <v>132340985</v>
       </c>
       <c r="B60" t="n">
         <v>57953</v>
@@ -6846,16 +6838,24 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>435511</v>
+        <v>435645</v>
       </c>
       <c r="R60" t="n">
-        <v>7009171</v>
+        <v>7009273</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6892,7 +6892,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Bohål ca 1,8 m upp i grantickerötad granhögstubbe.Öppning ca 4,5cm i diameter.Ganska färskt</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6919,7 +6919,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132340990</v>
+        <v>132340988</v>
       </c>
       <c r="B61" t="n">
         <v>57953</v>
@@ -6954,10 +6954,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>435589</v>
+        <v>435597</v>
       </c>
       <c r="R61" t="n">
-        <v>7009520</v>
+        <v>7009455</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7021,7 +7021,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132340965</v>
+        <v>132340990</v>
       </c>
       <c r="B62" t="n">
         <v>57953</v>
@@ -7056,10 +7056,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>435503</v>
+        <v>435589</v>
       </c>
       <c r="R62" t="n">
-        <v>7009162</v>
+        <v>7009520</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7123,7 +7123,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132340988</v>
+        <v>132340965</v>
       </c>
       <c r="B63" t="n">
         <v>57953</v>
@@ -7158,10 +7158,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>435597</v>
+        <v>435503</v>
       </c>
       <c r="R63" t="n">
-        <v>7009455</v>
+        <v>7009162</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7531,7 +7531,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132340975</v>
+        <v>132340958</v>
       </c>
       <c r="B67" t="n">
         <v>57953</v>
@@ -7566,10 +7566,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>435422</v>
+        <v>435594</v>
       </c>
       <c r="R67" t="n">
-        <v>7009269</v>
+        <v>7009012</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7633,7 +7633,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132340973</v>
+        <v>132340975</v>
       </c>
       <c r="B68" t="n">
         <v>57953</v>
@@ -7668,10 +7668,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>435536</v>
+        <v>435422</v>
       </c>
       <c r="R68" t="n">
-        <v>7009212</v>
+        <v>7009269</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7708,7 +7708,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7837,7 +7837,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132340958</v>
+        <v>132340973</v>
       </c>
       <c r="B70" t="n">
         <v>57953</v>
@@ -7872,10 +7872,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>435594</v>
+        <v>435536</v>
       </c>
       <c r="R70" t="n">
-        <v>7009012</v>
+        <v>7009212</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7912,7 +7912,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7939,7 +7939,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132340994</v>
+        <v>132340966</v>
       </c>
       <c r="B71" t="n">
         <v>57953</v>
@@ -7974,10 +7974,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>435648</v>
+        <v>435505</v>
       </c>
       <c r="R71" t="n">
-        <v>7009710</v>
+        <v>7009166</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8041,7 +8041,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132340966</v>
+        <v>132340994</v>
       </c>
       <c r="B72" t="n">
         <v>57953</v>
@@ -8076,10 +8076,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>435505</v>
+        <v>435648</v>
       </c>
       <c r="R72" t="n">
-        <v>7009166</v>
+        <v>7009710</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8116,7 +8116,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8245,7 +8245,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132340979</v>
+        <v>132340956</v>
       </c>
       <c r="B74" t="n">
         <v>57953</v>
@@ -8280,10 +8280,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>435416</v>
+        <v>435811</v>
       </c>
       <c r="R74" t="n">
-        <v>7009430</v>
+        <v>7009266</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8347,7 +8347,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132340956</v>
+        <v>132340979</v>
       </c>
       <c r="B75" t="n">
         <v>57953</v>
@@ -8382,10 +8382,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>435811</v>
+        <v>435416</v>
       </c>
       <c r="R75" t="n">
-        <v>7009266</v>
+        <v>7009430</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8554,7 +8554,7 @@
         <v>132341121</v>
       </c>
       <c r="B77" t="n">
-        <v>91904</v>
+        <v>91905</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8750,7 +8750,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132340961</v>
+        <v>132340991</v>
       </c>
       <c r="B79" t="n">
         <v>57953</v>
@@ -8785,10 +8785,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>435531</v>
+        <v>435608</v>
       </c>
       <c r="R79" t="n">
-        <v>7009066</v>
+        <v>7009554</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8825,7 +8825,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8852,7 +8852,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132340991</v>
+        <v>132340976</v>
       </c>
       <c r="B80" t="n">
         <v>57953</v>
@@ -8887,10 +8887,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>435608</v>
+        <v>435445</v>
       </c>
       <c r="R80" t="n">
-        <v>7009554</v>
+        <v>7009286</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8927,7 +8927,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8954,7 +8954,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132340987</v>
+        <v>132340961</v>
       </c>
       <c r="B81" t="n">
         <v>57953</v>
@@ -8989,10 +8989,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>435703</v>
+        <v>435531</v>
       </c>
       <c r="R81" t="n">
-        <v>7009319</v>
+        <v>7009066</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9056,7 +9056,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132340976</v>
+        <v>132340987</v>
       </c>
       <c r="B82" t="n">
         <v>57953</v>
@@ -9091,10 +9091,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>435445</v>
+        <v>435703</v>
       </c>
       <c r="R82" t="n">
-        <v>7009286</v>
+        <v>7009319</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9131,7 +9131,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9158,10 +9158,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132341120</v>
+        <v>132340978</v>
       </c>
       <c r="B83" t="n">
-        <v>91904</v>
+        <v>57953</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9169,21 +9169,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9193,10 +9193,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>435875</v>
+        <v>435358</v>
       </c>
       <c r="R83" t="n">
-        <v>7009285</v>
+        <v>7009404</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9229,6 +9229,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9357,10 +9362,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132340978</v>
+        <v>132341120</v>
       </c>
       <c r="B85" t="n">
-        <v>57953</v>
+        <v>91905</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9368,21 +9373,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9392,10 +9397,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>435358</v>
+        <v>435875</v>
       </c>
       <c r="R85" t="n">
-        <v>7009404</v>
+        <v>7009285</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9428,11 +9433,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9459,7 +9459,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132340959</v>
+        <v>132340969</v>
       </c>
       <c r="B86" t="n">
         <v>57953</v>
@@ -9494,10 +9494,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>435523</v>
+        <v>435503</v>
       </c>
       <c r="R86" t="n">
-        <v>7009035</v>
+        <v>7009197</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9561,7 +9561,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132340969</v>
+        <v>132340959</v>
       </c>
       <c r="B87" t="n">
         <v>57953</v>
@@ -9596,10 +9596,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>435503</v>
+        <v>435523</v>
       </c>
       <c r="R87" t="n">
-        <v>7009197</v>
+        <v>7009035</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9636,7 +9636,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD87" t="b">

--- a/artfynd/A 11380-2026 artfynd.xlsx
+++ b/artfynd/A 11380-2026 artfynd.xlsx
@@ -4863,7 +4863,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132340953</v>
+        <v>132340957</v>
       </c>
       <c r="B41" t="n">
         <v>57953</v>
@@ -4898,10 +4898,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>435992</v>
+        <v>435678</v>
       </c>
       <c r="R41" t="n">
-        <v>7009388</v>
+        <v>7009061</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4938,7 +4938,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5075,7 +5075,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132340957</v>
+        <v>132340953</v>
       </c>
       <c r="B43" t="n">
         <v>57953</v>
@@ -5110,10 +5110,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>435678</v>
+        <v>435992</v>
       </c>
       <c r="R43" t="n">
-        <v>7009061</v>
+        <v>7009388</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5150,7 +5150,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5177,7 +5177,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132340986</v>
+        <v>132340996</v>
       </c>
       <c r="B44" t="n">
         <v>57953</v>
@@ -5212,10 +5212,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>435632</v>
+        <v>435657</v>
       </c>
       <c r="R44" t="n">
-        <v>7009284</v>
+        <v>7009715</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5252,7 +5252,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5279,7 +5279,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132340996</v>
+        <v>132340977</v>
       </c>
       <c r="B45" t="n">
         <v>57953</v>
@@ -5314,10 +5314,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>435657</v>
+        <v>435438</v>
       </c>
       <c r="R45" t="n">
-        <v>7009715</v>
+        <v>7009287</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5381,7 +5381,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132340977</v>
+        <v>132340986</v>
       </c>
       <c r="B46" t="n">
         <v>57953</v>
@@ -5416,10 +5416,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>435438</v>
+        <v>435632</v>
       </c>
       <c r="R46" t="n">
-        <v>7009287</v>
+        <v>7009284</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5483,7 +5483,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132340983</v>
+        <v>132340997</v>
       </c>
       <c r="B47" t="n">
         <v>57953</v>
@@ -5518,10 +5518,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>435570</v>
+        <v>435714</v>
       </c>
       <c r="R47" t="n">
-        <v>7009342</v>
+        <v>7009769</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5558,7 +5558,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5585,7 +5585,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132340997</v>
+        <v>132340983</v>
       </c>
       <c r="B48" t="n">
         <v>57953</v>
@@ -5620,10 +5620,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>435714</v>
+        <v>435570</v>
       </c>
       <c r="R48" t="n">
-        <v>7009769</v>
+        <v>7009342</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5660,7 +5660,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6197,7 +6197,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132340984</v>
+        <v>132340989</v>
       </c>
       <c r="B54" t="n">
         <v>57953</v>
@@ -6232,10 +6232,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>435644</v>
+        <v>435579</v>
       </c>
       <c r="R54" t="n">
-        <v>7009260</v>
+        <v>7009462</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6299,7 +6299,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132340982</v>
+        <v>132340984</v>
       </c>
       <c r="B55" t="n">
         <v>57953</v>
@@ -6334,10 +6334,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>435574</v>
+        <v>435644</v>
       </c>
       <c r="R55" t="n">
-        <v>7009351</v>
+        <v>7009260</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6374,7 +6374,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6503,7 +6503,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132340989</v>
+        <v>132340982</v>
       </c>
       <c r="B57" t="n">
         <v>57953</v>
@@ -6538,10 +6538,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>435579</v>
+        <v>435574</v>
       </c>
       <c r="R57" t="n">
-        <v>7009462</v>
+        <v>7009351</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6605,7 +6605,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132340968</v>
+        <v>132340967</v>
       </c>
       <c r="B58" t="n">
         <v>57953</v>
@@ -6640,10 +6640,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>435492</v>
+        <v>435511</v>
       </c>
       <c r="R58" t="n">
-        <v>7009187</v>
+        <v>7009171</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6707,7 +6707,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132340967</v>
+        <v>132340985</v>
       </c>
       <c r="B59" t="n">
         <v>57953</v>
@@ -6736,16 +6736,24 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>435511</v>
+        <v>435645</v>
       </c>
       <c r="R59" t="n">
-        <v>7009171</v>
+        <v>7009273</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6782,7 +6790,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Bohål ca 1,8 m upp i grantickerötad granhögstubbe.Öppning ca 4,5cm i diameter.Ganska färskt</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6809,7 +6817,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132340985</v>
+        <v>132340968</v>
       </c>
       <c r="B60" t="n">
         <v>57953</v>
@@ -6838,24 +6846,16 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>435645</v>
+        <v>435492</v>
       </c>
       <c r="R60" t="n">
-        <v>7009273</v>
+        <v>7009187</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6892,7 +6892,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Bohål ca 1,8 m upp i grantickerötad granhögstubbe.Öppning ca 4,5cm i diameter.Ganska färskt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6919,7 +6919,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132340988</v>
+        <v>132340990</v>
       </c>
       <c r="B61" t="n">
         <v>57953</v>
@@ -6954,10 +6954,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>435597</v>
+        <v>435589</v>
       </c>
       <c r="R61" t="n">
-        <v>7009455</v>
+        <v>7009520</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7021,7 +7021,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132340990</v>
+        <v>132340988</v>
       </c>
       <c r="B62" t="n">
         <v>57953</v>
@@ -7056,10 +7056,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>435589</v>
+        <v>435597</v>
       </c>
       <c r="R62" t="n">
-        <v>7009520</v>
+        <v>7009455</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7531,7 +7531,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132340958</v>
+        <v>132340973</v>
       </c>
       <c r="B67" t="n">
         <v>57953</v>
@@ -7566,10 +7566,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>435594</v>
+        <v>435536</v>
       </c>
       <c r="R67" t="n">
-        <v>7009012</v>
+        <v>7009212</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7606,7 +7606,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7633,7 +7633,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132340975</v>
+        <v>132340955</v>
       </c>
       <c r="B68" t="n">
         <v>57953</v>
@@ -7668,10 +7668,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>435422</v>
+        <v>435814</v>
       </c>
       <c r="R68" t="n">
-        <v>7009269</v>
+        <v>7009258</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7708,7 +7708,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7735,7 +7735,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132340955</v>
+        <v>132340975</v>
       </c>
       <c r="B69" t="n">
         <v>57953</v>
@@ -7770,10 +7770,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>435814</v>
+        <v>435422</v>
       </c>
       <c r="R69" t="n">
-        <v>7009258</v>
+        <v>7009269</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7810,7 +7810,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7837,7 +7837,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132340973</v>
+        <v>132340958</v>
       </c>
       <c r="B70" t="n">
         <v>57953</v>
@@ -7872,10 +7872,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>435536</v>
+        <v>435594</v>
       </c>
       <c r="R70" t="n">
-        <v>7009212</v>
+        <v>7009012</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7912,7 +7912,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7939,7 +7939,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132340966</v>
+        <v>132340998</v>
       </c>
       <c r="B71" t="n">
         <v>57953</v>
@@ -7974,10 +7974,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>435505</v>
+        <v>435702</v>
       </c>
       <c r="R71" t="n">
-        <v>7009166</v>
+        <v>7009759</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8143,7 +8143,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132340998</v>
+        <v>132340966</v>
       </c>
       <c r="B73" t="n">
         <v>57953</v>
@@ -8178,10 +8178,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>435702</v>
+        <v>435505</v>
       </c>
       <c r="R73" t="n">
-        <v>7009759</v>
+        <v>7009166</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8218,7 +8218,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8245,7 +8245,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132340956</v>
+        <v>132340979</v>
       </c>
       <c r="B74" t="n">
         <v>57953</v>
@@ -8280,10 +8280,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>435811</v>
+        <v>435416</v>
       </c>
       <c r="R74" t="n">
-        <v>7009266</v>
+        <v>7009430</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8347,7 +8347,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132340979</v>
+        <v>132340956</v>
       </c>
       <c r="B75" t="n">
         <v>57953</v>
@@ -8382,10 +8382,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>435416</v>
+        <v>435811</v>
       </c>
       <c r="R75" t="n">
-        <v>7009430</v>
+        <v>7009266</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8750,7 +8750,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132340991</v>
+        <v>132340987</v>
       </c>
       <c r="B79" t="n">
         <v>57953</v>
@@ -8785,10 +8785,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>435608</v>
+        <v>435703</v>
       </c>
       <c r="R79" t="n">
-        <v>7009554</v>
+        <v>7009319</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8852,7 +8852,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132340976</v>
+        <v>132340961</v>
       </c>
       <c r="B80" t="n">
         <v>57953</v>
@@ -8887,10 +8887,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>435445</v>
+        <v>435531</v>
       </c>
       <c r="R80" t="n">
-        <v>7009286</v>
+        <v>7009066</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8954,7 +8954,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132340961</v>
+        <v>132340991</v>
       </c>
       <c r="B81" t="n">
         <v>57953</v>
@@ -8989,10 +8989,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>435531</v>
+        <v>435608</v>
       </c>
       <c r="R81" t="n">
-        <v>7009066</v>
+        <v>7009554</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9056,7 +9056,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132340987</v>
+        <v>132340976</v>
       </c>
       <c r="B82" t="n">
         <v>57953</v>
@@ -9091,10 +9091,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>435703</v>
+        <v>435445</v>
       </c>
       <c r="R82" t="n">
-        <v>7009319</v>
+        <v>7009286</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9131,7 +9131,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD82" t="b">

--- a/artfynd/A 11380-2026 artfynd.xlsx
+++ b/artfynd/A 11380-2026 artfynd.xlsx
@@ -4863,7 +4863,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132340957</v>
+        <v>132340953</v>
       </c>
       <c r="B41" t="n">
         <v>57953</v>
@@ -4898,10 +4898,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>435678</v>
+        <v>435992</v>
       </c>
       <c r="R41" t="n">
-        <v>7009061</v>
+        <v>7009388</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4938,7 +4938,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5075,7 +5075,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132340953</v>
+        <v>132340957</v>
       </c>
       <c r="B43" t="n">
         <v>57953</v>
@@ -5110,10 +5110,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>435992</v>
+        <v>435678</v>
       </c>
       <c r="R43" t="n">
-        <v>7009388</v>
+        <v>7009061</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5150,7 +5150,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5177,7 +5177,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132340996</v>
+        <v>132340986</v>
       </c>
       <c r="B44" t="n">
         <v>57953</v>
@@ -5212,10 +5212,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>435657</v>
+        <v>435632</v>
       </c>
       <c r="R44" t="n">
-        <v>7009715</v>
+        <v>7009284</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5252,7 +5252,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5279,7 +5279,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132340977</v>
+        <v>132340996</v>
       </c>
       <c r="B45" t="n">
         <v>57953</v>
@@ -5314,10 +5314,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>435438</v>
+        <v>435657</v>
       </c>
       <c r="R45" t="n">
-        <v>7009287</v>
+        <v>7009715</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5381,7 +5381,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132340986</v>
+        <v>132340977</v>
       </c>
       <c r="B46" t="n">
         <v>57953</v>
@@ -5416,10 +5416,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>435632</v>
+        <v>435438</v>
       </c>
       <c r="R46" t="n">
-        <v>7009284</v>
+        <v>7009287</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5483,7 +5483,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132340997</v>
+        <v>132340983</v>
       </c>
       <c r="B47" t="n">
         <v>57953</v>
@@ -5518,10 +5518,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>435714</v>
+        <v>435570</v>
       </c>
       <c r="R47" t="n">
-        <v>7009769</v>
+        <v>7009342</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5558,7 +5558,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5585,7 +5585,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132340983</v>
+        <v>132340997</v>
       </c>
       <c r="B48" t="n">
         <v>57953</v>
@@ -5620,10 +5620,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>435570</v>
+        <v>435714</v>
       </c>
       <c r="R48" t="n">
-        <v>7009342</v>
+        <v>7009769</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5660,7 +5660,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6197,7 +6197,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132340989</v>
+        <v>132340984</v>
       </c>
       <c r="B54" t="n">
         <v>57953</v>
@@ -6232,10 +6232,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>435579</v>
+        <v>435644</v>
       </c>
       <c r="R54" t="n">
-        <v>7009462</v>
+        <v>7009260</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6299,7 +6299,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132340984</v>
+        <v>132340982</v>
       </c>
       <c r="B55" t="n">
         <v>57953</v>
@@ -6334,10 +6334,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>435644</v>
+        <v>435574</v>
       </c>
       <c r="R55" t="n">
-        <v>7009260</v>
+        <v>7009351</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6374,7 +6374,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6503,7 +6503,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132340982</v>
+        <v>132340989</v>
       </c>
       <c r="B57" t="n">
         <v>57953</v>
@@ -6538,10 +6538,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>435574</v>
+        <v>435579</v>
       </c>
       <c r="R57" t="n">
-        <v>7009351</v>
+        <v>7009462</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6605,7 +6605,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132340967</v>
+        <v>132340968</v>
       </c>
       <c r="B58" t="n">
         <v>57953</v>
@@ -6640,10 +6640,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>435511</v>
+        <v>435492</v>
       </c>
       <c r="R58" t="n">
-        <v>7009171</v>
+        <v>7009187</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6707,7 +6707,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132340985</v>
+        <v>132340967</v>
       </c>
       <c r="B59" t="n">
         <v>57953</v>
@@ -6736,24 +6736,16 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>435645</v>
+        <v>435511</v>
       </c>
       <c r="R59" t="n">
-        <v>7009273</v>
+        <v>7009171</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6790,7 +6782,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Bohål ca 1,8 m upp i grantickerötad granhögstubbe.Öppning ca 4,5cm i diameter.Ganska färskt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6817,7 +6809,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132340968</v>
+        <v>132340985</v>
       </c>
       <c r="B60" t="n">
         <v>57953</v>
@@ -6846,16 +6838,24 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>435492</v>
+        <v>435645</v>
       </c>
       <c r="R60" t="n">
-        <v>7009187</v>
+        <v>7009273</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6892,7 +6892,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Bohål ca 1,8 m upp i grantickerötad granhögstubbe.Öppning ca 4,5cm i diameter.Ganska färskt</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6919,7 +6919,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132340990</v>
+        <v>132340988</v>
       </c>
       <c r="B61" t="n">
         <v>57953</v>
@@ -6954,10 +6954,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>435589</v>
+        <v>435597</v>
       </c>
       <c r="R61" t="n">
-        <v>7009520</v>
+        <v>7009455</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7021,7 +7021,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132340988</v>
+        <v>132340965</v>
       </c>
       <c r="B62" t="n">
         <v>57953</v>
@@ -7056,10 +7056,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>435597</v>
+        <v>435503</v>
       </c>
       <c r="R62" t="n">
-        <v>7009455</v>
+        <v>7009162</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7123,7 +7123,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132340965</v>
+        <v>132340990</v>
       </c>
       <c r="B63" t="n">
         <v>57953</v>
@@ -7158,10 +7158,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>435503</v>
+        <v>435589</v>
       </c>
       <c r="R63" t="n">
-        <v>7009162</v>
+        <v>7009520</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7531,7 +7531,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132340973</v>
+        <v>132340958</v>
       </c>
       <c r="B67" t="n">
         <v>57953</v>
@@ -7566,10 +7566,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>435536</v>
+        <v>435594</v>
       </c>
       <c r="R67" t="n">
-        <v>7009212</v>
+        <v>7009012</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7606,7 +7606,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7633,7 +7633,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132340955</v>
+        <v>132340975</v>
       </c>
       <c r="B68" t="n">
         <v>57953</v>
@@ -7668,10 +7668,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>435814</v>
+        <v>435422</v>
       </c>
       <c r="R68" t="n">
-        <v>7009258</v>
+        <v>7009269</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7708,7 +7708,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7735,7 +7735,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132340975</v>
+        <v>132340955</v>
       </c>
       <c r="B69" t="n">
         <v>57953</v>
@@ -7770,10 +7770,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>435422</v>
+        <v>435814</v>
       </c>
       <c r="R69" t="n">
-        <v>7009269</v>
+        <v>7009258</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7810,7 +7810,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7837,7 +7837,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132340958</v>
+        <v>132340973</v>
       </c>
       <c r="B70" t="n">
         <v>57953</v>
@@ -7872,10 +7872,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>435594</v>
+        <v>435536</v>
       </c>
       <c r="R70" t="n">
-        <v>7009012</v>
+        <v>7009212</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7912,7 +7912,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7939,7 +7939,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132340998</v>
+        <v>132340994</v>
       </c>
       <c r="B71" t="n">
         <v>57953</v>
@@ -7974,10 +7974,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>435702</v>
+        <v>435648</v>
       </c>
       <c r="R71" t="n">
-        <v>7009759</v>
+        <v>7009710</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8041,7 +8041,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132340994</v>
+        <v>132340998</v>
       </c>
       <c r="B72" t="n">
         <v>57953</v>
@@ -8076,10 +8076,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>435648</v>
+        <v>435702</v>
       </c>
       <c r="R72" t="n">
-        <v>7009710</v>
+        <v>7009759</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8245,7 +8245,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132340979</v>
+        <v>132340956</v>
       </c>
       <c r="B74" t="n">
         <v>57953</v>
@@ -8280,10 +8280,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>435416</v>
+        <v>435811</v>
       </c>
       <c r="R74" t="n">
-        <v>7009430</v>
+        <v>7009266</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8347,7 +8347,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132340956</v>
+        <v>132340979</v>
       </c>
       <c r="B75" t="n">
         <v>57953</v>
@@ -8382,10 +8382,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>435811</v>
+        <v>435416</v>
       </c>
       <c r="R75" t="n">
-        <v>7009266</v>
+        <v>7009430</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8551,10 +8551,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132341121</v>
+        <v>132340952</v>
       </c>
       <c r="B77" t="n">
-        <v>91905</v>
+        <v>57953</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8562,21 +8562,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>435520</v>
+        <v>435863</v>
       </c>
       <c r="R77" t="n">
-        <v>7009134</v>
+        <v>7009504</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8622,6 +8622,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8648,10 +8653,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132340952</v>
+        <v>132341121</v>
       </c>
       <c r="B78" t="n">
-        <v>57953</v>
+        <v>91905</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8659,21 +8664,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8683,10 +8688,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>435863</v>
+        <v>435520</v>
       </c>
       <c r="R78" t="n">
-        <v>7009504</v>
+        <v>7009134</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8719,11 +8724,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8750,7 +8750,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132340987</v>
+        <v>132340976</v>
       </c>
       <c r="B79" t="n">
         <v>57953</v>
@@ -8785,10 +8785,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>435703</v>
+        <v>435445</v>
       </c>
       <c r="R79" t="n">
-        <v>7009319</v>
+        <v>7009286</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8825,7 +8825,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8954,7 +8954,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132340991</v>
+        <v>132340987</v>
       </c>
       <c r="B81" t="n">
         <v>57953</v>
@@ -8989,10 +8989,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>435608</v>
+        <v>435703</v>
       </c>
       <c r="R81" t="n">
-        <v>7009554</v>
+        <v>7009319</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9056,7 +9056,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132340976</v>
+        <v>132340991</v>
       </c>
       <c r="B82" t="n">
         <v>57953</v>
@@ -9091,10 +9091,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>435445</v>
+        <v>435608</v>
       </c>
       <c r="R82" t="n">
-        <v>7009286</v>
+        <v>7009554</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9131,7 +9131,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9158,10 +9158,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132340978</v>
+        <v>132341120</v>
       </c>
       <c r="B83" t="n">
-        <v>57953</v>
+        <v>91905</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9169,21 +9169,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9193,10 +9193,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>435358</v>
+        <v>435875</v>
       </c>
       <c r="R83" t="n">
-        <v>7009404</v>
+        <v>7009285</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9229,11 +9229,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9260,7 +9255,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132340951</v>
+        <v>132340978</v>
       </c>
       <c r="B84" t="n">
         <v>57953</v>
@@ -9295,10 +9290,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>435770</v>
+        <v>435358</v>
       </c>
       <c r="R84" t="n">
-        <v>7009576</v>
+        <v>7009404</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9362,10 +9357,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132341120</v>
+        <v>132340951</v>
       </c>
       <c r="B85" t="n">
-        <v>91905</v>
+        <v>57953</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9373,21 +9368,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9397,10 +9392,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>435875</v>
+        <v>435770</v>
       </c>
       <c r="R85" t="n">
-        <v>7009285</v>
+        <v>7009576</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9433,6 +9428,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD85" t="b">

--- a/artfynd/A 11380-2026 artfynd.xlsx
+++ b/artfynd/A 11380-2026 artfynd.xlsx
@@ -8551,10 +8551,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132340952</v>
+        <v>132341121</v>
       </c>
       <c r="B77" t="n">
-        <v>57953</v>
+        <v>91905</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8562,21 +8562,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>435863</v>
+        <v>435520</v>
       </c>
       <c r="R77" t="n">
-        <v>7009504</v>
+        <v>7009134</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8622,11 +8622,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8653,10 +8648,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132341121</v>
+        <v>132340952</v>
       </c>
       <c r="B78" t="n">
-        <v>91905</v>
+        <v>57953</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8664,21 +8659,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8688,10 +8683,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>435520</v>
+        <v>435863</v>
       </c>
       <c r="R78" t="n">
-        <v>7009134</v>
+        <v>7009504</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8724,6 +8719,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">

--- a/artfynd/A 11380-2026 artfynd.xlsx
+++ b/artfynd/A 11380-2026 artfynd.xlsx
@@ -4764,7 +4764,7 @@
         <v>132340980</v>
       </c>
       <c r="B40" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4863,10 +4863,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132340953</v>
+        <v>132340957</v>
       </c>
       <c r="B41" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4898,10 +4898,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>435992</v>
+        <v>435678</v>
       </c>
       <c r="R41" t="n">
-        <v>7009388</v>
+        <v>7009061</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4938,7 +4938,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4968,7 +4968,7 @@
         <v>132340964</v>
       </c>
       <c r="B42" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5075,10 +5075,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132340957</v>
+        <v>132340953</v>
       </c>
       <c r="B43" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5110,10 +5110,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>435678</v>
+        <v>435992</v>
       </c>
       <c r="R43" t="n">
-        <v>7009061</v>
+        <v>7009388</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5150,7 +5150,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5177,10 +5177,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132340986</v>
+        <v>132340996</v>
       </c>
       <c r="B44" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5212,10 +5212,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>435632</v>
+        <v>435657</v>
       </c>
       <c r="R44" t="n">
-        <v>7009284</v>
+        <v>7009715</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5252,7 +5252,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5279,10 +5279,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132340996</v>
+        <v>132340977</v>
       </c>
       <c r="B45" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5314,10 +5314,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>435657</v>
+        <v>435438</v>
       </c>
       <c r="R45" t="n">
-        <v>7009715</v>
+        <v>7009287</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5381,10 +5381,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132340977</v>
+        <v>132340986</v>
       </c>
       <c r="B46" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5416,10 +5416,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>435438</v>
+        <v>435632</v>
       </c>
       <c r="R46" t="n">
-        <v>7009287</v>
+        <v>7009284</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5483,10 +5483,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132340983</v>
+        <v>132340962</v>
       </c>
       <c r="B47" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5518,10 +5518,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>435570</v>
+        <v>435540</v>
       </c>
       <c r="R47" t="n">
-        <v>7009342</v>
+        <v>7009069</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5588,7 +5588,7 @@
         <v>132340997</v>
       </c>
       <c r="B48" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5687,10 +5687,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132340974</v>
+        <v>132340983</v>
       </c>
       <c r="B49" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5722,10 +5722,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>435472</v>
+        <v>435570</v>
       </c>
       <c r="R49" t="n">
-        <v>7009247</v>
+        <v>7009342</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5789,10 +5789,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132340962</v>
+        <v>132340974</v>
       </c>
       <c r="B50" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5824,10 +5824,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>435540</v>
+        <v>435472</v>
       </c>
       <c r="R50" t="n">
-        <v>7009069</v>
+        <v>7009247</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5864,7 +5864,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5894,7 +5894,7 @@
         <v>132340970</v>
       </c>
       <c r="B51" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5996,7 +5996,7 @@
         <v>132340995</v>
       </c>
       <c r="B52" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>132340971</v>
       </c>
       <c r="B53" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6197,10 +6197,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132340984</v>
+        <v>132340989</v>
       </c>
       <c r="B54" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6232,10 +6232,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>435644</v>
+        <v>435579</v>
       </c>
       <c r="R54" t="n">
-        <v>7009260</v>
+        <v>7009462</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6299,10 +6299,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132340982</v>
+        <v>132340984</v>
       </c>
       <c r="B55" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6334,10 +6334,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>435574</v>
+        <v>435644</v>
       </c>
       <c r="R55" t="n">
-        <v>7009351</v>
+        <v>7009260</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6374,7 +6374,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6404,7 +6404,7 @@
         <v>132340992</v>
       </c>
       <c r="B56" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6503,10 +6503,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132340989</v>
+        <v>132340982</v>
       </c>
       <c r="B57" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6538,10 +6538,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>435579</v>
+        <v>435574</v>
       </c>
       <c r="R57" t="n">
-        <v>7009462</v>
+        <v>7009351</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6605,10 +6605,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132340968</v>
+        <v>132340967</v>
       </c>
       <c r="B58" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6640,10 +6640,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>435492</v>
+        <v>435511</v>
       </c>
       <c r="R58" t="n">
-        <v>7009187</v>
+        <v>7009171</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6707,10 +6707,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132340967</v>
+        <v>132340985</v>
       </c>
       <c r="B59" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6736,16 +6736,24 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>435511</v>
+        <v>435645</v>
       </c>
       <c r="R59" t="n">
-        <v>7009171</v>
+        <v>7009273</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6782,7 +6790,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Bohål ca 1,8 m upp i grantickerötad granhögstubbe.Öppning ca 4,5cm i diameter.Ganska färskt</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6809,10 +6817,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132340985</v>
+        <v>132340968</v>
       </c>
       <c r="B60" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6838,24 +6846,16 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>435645</v>
+        <v>435492</v>
       </c>
       <c r="R60" t="n">
-        <v>7009273</v>
+        <v>7009187</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6892,7 +6892,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Bohål ca 1,8 m upp i grantickerötad granhögstubbe.Öppning ca 4,5cm i diameter.Ganska färskt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6919,10 +6919,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132340988</v>
+        <v>132340990</v>
       </c>
       <c r="B61" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6954,10 +6954,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>435597</v>
+        <v>435589</v>
       </c>
       <c r="R61" t="n">
-        <v>7009455</v>
+        <v>7009520</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7021,10 +7021,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132340965</v>
+        <v>132340988</v>
       </c>
       <c r="B62" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7056,10 +7056,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>435503</v>
+        <v>435597</v>
       </c>
       <c r="R62" t="n">
-        <v>7009162</v>
+        <v>7009455</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7123,10 +7123,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132340990</v>
+        <v>132340965</v>
       </c>
       <c r="B63" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7158,10 +7158,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>435589</v>
+        <v>435503</v>
       </c>
       <c r="R63" t="n">
-        <v>7009520</v>
+        <v>7009162</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7228,7 +7228,7 @@
         <v>132340963</v>
       </c>
       <c r="B64" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         <v>132340972</v>
       </c>
       <c r="B65" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7432,7 +7432,7 @@
         <v>132340960</v>
       </c>
       <c r="B66" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7531,10 +7531,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132340958</v>
+        <v>132340973</v>
       </c>
       <c r="B67" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7566,10 +7566,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>435594</v>
+        <v>435536</v>
       </c>
       <c r="R67" t="n">
-        <v>7009012</v>
+        <v>7009212</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7606,7 +7606,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7633,10 +7633,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132340975</v>
+        <v>132340955</v>
       </c>
       <c r="B68" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7668,10 +7668,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>435422</v>
+        <v>435814</v>
       </c>
       <c r="R68" t="n">
-        <v>7009269</v>
+        <v>7009258</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7708,7 +7708,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7735,10 +7735,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132340955</v>
+        <v>132340975</v>
       </c>
       <c r="B69" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7770,10 +7770,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>435814</v>
+        <v>435422</v>
       </c>
       <c r="R69" t="n">
-        <v>7009258</v>
+        <v>7009269</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7810,7 +7810,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7837,10 +7837,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132340973</v>
+        <v>132340958</v>
       </c>
       <c r="B70" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7872,10 +7872,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>435536</v>
+        <v>435594</v>
       </c>
       <c r="R70" t="n">
-        <v>7009212</v>
+        <v>7009012</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7912,7 +7912,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7939,10 +7939,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132340994</v>
+        <v>132340998</v>
       </c>
       <c r="B71" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7974,10 +7974,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>435648</v>
+        <v>435702</v>
       </c>
       <c r="R71" t="n">
-        <v>7009710</v>
+        <v>7009759</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8041,10 +8041,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132340998</v>
+        <v>132340994</v>
       </c>
       <c r="B72" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8076,10 +8076,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>435702</v>
+        <v>435648</v>
       </c>
       <c r="R72" t="n">
-        <v>7009759</v>
+        <v>7009710</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8146,7 +8146,7 @@
         <v>132340966</v>
       </c>
       <c r="B73" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8245,10 +8245,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132340956</v>
+        <v>132340979</v>
       </c>
       <c r="B74" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8280,10 +8280,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>435811</v>
+        <v>435416</v>
       </c>
       <c r="R74" t="n">
-        <v>7009266</v>
+        <v>7009430</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8347,10 +8347,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132340979</v>
+        <v>132340956</v>
       </c>
       <c r="B75" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8382,10 +8382,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>435416</v>
+        <v>435811</v>
       </c>
       <c r="R75" t="n">
-        <v>7009430</v>
+        <v>7009266</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8452,7 +8452,7 @@
         <v>132340954</v>
       </c>
       <c r="B76" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8554,7 +8554,7 @@
         <v>132341121</v>
       </c>
       <c r="B77" t="n">
-        <v>91905</v>
+        <v>91906</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8651,7 +8651,7 @@
         <v>132340952</v>
       </c>
       <c r="B78" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8750,10 +8750,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132340976</v>
+        <v>132340987</v>
       </c>
       <c r="B79" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8785,10 +8785,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>435445</v>
+        <v>435703</v>
       </c>
       <c r="R79" t="n">
-        <v>7009286</v>
+        <v>7009319</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8825,7 +8825,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8855,7 +8855,7 @@
         <v>132340961</v>
       </c>
       <c r="B80" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8954,10 +8954,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132340987</v>
+        <v>132340991</v>
       </c>
       <c r="B81" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8989,10 +8989,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>435703</v>
+        <v>435608</v>
       </c>
       <c r="R81" t="n">
-        <v>7009319</v>
+        <v>7009554</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9056,10 +9056,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132340991</v>
+        <v>132340976</v>
       </c>
       <c r="B82" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9091,10 +9091,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>435608</v>
+        <v>435445</v>
       </c>
       <c r="R82" t="n">
-        <v>7009554</v>
+        <v>7009286</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9131,7 +9131,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9161,7 +9161,7 @@
         <v>132341120</v>
       </c>
       <c r="B83" t="n">
-        <v>91905</v>
+        <v>91906</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         <v>132340978</v>
       </c>
       <c r="B84" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         <v>132340951</v>
       </c>
       <c r="B85" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9462,7 +9462,7 @@
         <v>132340969</v>
       </c>
       <c r="B86" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9564,7 +9564,7 @@
         <v>132340959</v>
       </c>
       <c r="B87" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 11380-2026 artfynd.xlsx
+++ b/artfynd/A 11380-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY91"/>
+  <dimension ref="A1:AY96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121291899</v>
+        <v>132341120</v>
       </c>
       <c r="B2" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91970</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>436090</v>
+        <v>435875</v>
       </c>
       <c r="R2" t="n">
-        <v>7009214</v>
+        <v>7009285</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121291892</v>
+        <v>132341121</v>
       </c>
       <c r="B3" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91970</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>435750</v>
+        <v>435520</v>
       </c>
       <c r="R3" t="n">
-        <v>7009172</v>
+        <v>7009134</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,17 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121291909</v>
+        <v>133454055</v>
       </c>
       <c r="B4" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91970</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>435794</v>
+        <v>435564</v>
       </c>
       <c r="R4" t="n">
-        <v>7009569</v>
+        <v>7008805</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,17 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ringhack färska</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121291906</v>
+        <v>121291854</v>
       </c>
       <c r="B5" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>435791</v>
+        <v>435647</v>
       </c>
       <c r="R5" t="n">
-        <v>7009510</v>
+        <v>7009072</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1041,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,15 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121291889</v>
+        <v>121291869</v>
       </c>
       <c r="B6" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>435612</v>
+        <v>435758</v>
       </c>
       <c r="R6" t="n">
-        <v>7009186</v>
+        <v>7008887</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1143,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,15 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121291881</v>
+        <v>121291870</v>
       </c>
       <c r="B7" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1250,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>435608</v>
+        <v>435732</v>
       </c>
       <c r="R7" t="n">
-        <v>7009099</v>
+        <v>7008877</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,15 +1272,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121291900</v>
+        <v>121291871</v>
       </c>
       <c r="B8" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436083</v>
+        <v>435690</v>
       </c>
       <c r="R8" t="n">
-        <v>7009262</v>
+        <v>7008974</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1347,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,15 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121291874</v>
+        <v>121291872</v>
       </c>
       <c r="B9" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>435641</v>
+        <v>435678</v>
       </c>
       <c r="R9" t="n">
-        <v>7009054</v>
+        <v>7009063</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1531,15 +1476,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121291903</v>
+        <v>121291873</v>
       </c>
       <c r="B10" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,10 +1511,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436023</v>
+        <v>435658</v>
       </c>
       <c r="R10" t="n">
-        <v>7009315</v>
+        <v>7009058</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1551,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,15 +1578,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121291907</v>
+        <v>121291874</v>
       </c>
       <c r="B11" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1678,10 +1613,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>435736</v>
+        <v>435641</v>
       </c>
       <c r="R11" t="n">
-        <v>7009605</v>
+        <v>7009054</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1653,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,15 +1680,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121291896</v>
+        <v>121291875</v>
       </c>
       <c r="B12" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1785,10 +1715,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>435967</v>
+        <v>435652</v>
       </c>
       <c r="R12" t="n">
-        <v>7009242</v>
+        <v>7009067</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1852,15 +1782,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121291873</v>
+        <v>121291876</v>
       </c>
       <c r="B13" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1892,10 +1817,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>435658</v>
+        <v>435652</v>
       </c>
       <c r="R13" t="n">
-        <v>7009058</v>
+        <v>7009070</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1959,15 +1884,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121291901</v>
+        <v>121291877</v>
       </c>
       <c r="B14" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1999,10 +1919,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436078</v>
+        <v>435633</v>
       </c>
       <c r="R14" t="n">
-        <v>7009258</v>
+        <v>7009096</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2039,7 +1959,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,15 +1986,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121291898</v>
+        <v>121291878</v>
       </c>
       <c r="B15" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2106,10 +2021,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436097</v>
+        <v>435628</v>
       </c>
       <c r="R15" t="n">
-        <v>7009206</v>
+        <v>7009113</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2146,7 +2061,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,15 +2088,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121291884</v>
+        <v>121291879</v>
       </c>
       <c r="B16" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,10 +2123,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>435594</v>
+        <v>435627</v>
       </c>
       <c r="R16" t="n">
-        <v>7009120</v>
+        <v>7009109</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2280,15 +2190,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121291891</v>
+        <v>121291880</v>
       </c>
       <c r="B17" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2320,10 +2225,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>435678</v>
+        <v>435616</v>
       </c>
       <c r="R17" t="n">
-        <v>7009233</v>
+        <v>7009098</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2360,7 +2265,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,15 +2292,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121291888</v>
+        <v>121291881</v>
       </c>
       <c r="B18" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2427,10 +2327,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>435575</v>
+        <v>435608</v>
       </c>
       <c r="R18" t="n">
-        <v>7009163</v>
+        <v>7009099</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2467,7 +2367,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,15 +2394,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121291904</v>
+        <v>121291882</v>
       </c>
       <c r="B19" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2534,10 +2429,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>436021</v>
+        <v>435596</v>
       </c>
       <c r="R19" t="n">
-        <v>7009316</v>
+        <v>7009097</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2574,7 +2469,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2601,15 +2496,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121291887</v>
+        <v>121291883</v>
       </c>
       <c r="B20" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2641,10 +2531,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>435592</v>
+        <v>435583</v>
       </c>
       <c r="R20" t="n">
-        <v>7009143</v>
+        <v>7009115</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2681,7 +2571,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2708,15 +2598,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121291902</v>
+        <v>121291884</v>
       </c>
       <c r="B21" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2748,10 +2633,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436067</v>
+        <v>435594</v>
       </c>
       <c r="R21" t="n">
-        <v>7009258</v>
+        <v>7009120</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2815,15 +2700,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121291872</v>
+        <v>121291885</v>
       </c>
       <c r="B22" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2855,10 +2735,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>435678</v>
+        <v>435597</v>
       </c>
       <c r="R22" t="n">
-        <v>7009063</v>
+        <v>7009138</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2895,7 +2775,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2925,12 +2805,7 @@
         <v>121291886</v>
       </c>
       <c r="B23" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3049,15 +2924,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121291893</v>
+        <v>121291887</v>
       </c>
       <c r="B24" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3089,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>435799</v>
+        <v>435592</v>
       </c>
       <c r="R24" t="n">
-        <v>7009209</v>
+        <v>7009143</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3129,7 +2999,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3156,15 +3026,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121291897</v>
+        <v>121291888</v>
       </c>
       <c r="B25" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3196,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>435992</v>
+        <v>435575</v>
       </c>
       <c r="R25" t="n">
-        <v>7009245</v>
+        <v>7009163</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3236,7 +3101,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3263,15 +3128,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121291879</v>
+        <v>121291889</v>
       </c>
       <c r="B26" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3303,10 +3163,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>435627</v>
+        <v>435612</v>
       </c>
       <c r="R26" t="n">
-        <v>7009109</v>
+        <v>7009186</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3370,15 +3230,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121291883</v>
+        <v>121291890</v>
       </c>
       <c r="B27" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3410,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>435583</v>
+        <v>435679</v>
       </c>
       <c r="R27" t="n">
-        <v>7009115</v>
+        <v>7009239</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3450,7 +3305,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3477,15 +3332,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121291877</v>
+        <v>121291891</v>
       </c>
       <c r="B28" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3517,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>435633</v>
+        <v>435678</v>
       </c>
       <c r="R28" t="n">
-        <v>7009096</v>
+        <v>7009233</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3557,7 +3407,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3584,15 +3434,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121291908</v>
+        <v>121291892</v>
       </c>
       <c r="B29" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3624,10 +3469,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>435738</v>
+        <v>435750</v>
       </c>
       <c r="R29" t="n">
-        <v>7009628</v>
+        <v>7009172</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3691,15 +3536,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121291882</v>
+        <v>121291893</v>
       </c>
       <c r="B30" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3731,10 +3571,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>435596</v>
+        <v>435799</v>
       </c>
       <c r="R30" t="n">
-        <v>7009097</v>
+        <v>7009209</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3771,7 +3611,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3798,15 +3638,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121291905</v>
+        <v>121291894</v>
       </c>
       <c r="B31" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3838,10 +3673,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>435923</v>
+        <v>435823</v>
       </c>
       <c r="R31" t="n">
-        <v>7009425</v>
+        <v>7009195</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3905,15 +3740,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121291871</v>
+        <v>121291896</v>
       </c>
       <c r="B32" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3945,10 +3775,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>435690</v>
+        <v>435967</v>
       </c>
       <c r="R32" t="n">
-        <v>7008974</v>
+        <v>7009242</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3985,7 +3815,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4012,15 +3842,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121291890</v>
+        <v>121291897</v>
       </c>
       <c r="B33" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4052,10 +3877,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>435679</v>
+        <v>435992</v>
       </c>
       <c r="R33" t="n">
-        <v>7009239</v>
+        <v>7009245</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4092,7 +3917,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4119,15 +3944,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121291878</v>
+        <v>121291898</v>
       </c>
       <c r="B34" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4159,10 +3979,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>435628</v>
+        <v>436097</v>
       </c>
       <c r="R34" t="n">
-        <v>7009113</v>
+        <v>7009206</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4199,7 +4019,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4226,15 +4046,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121291880</v>
+        <v>121291899</v>
       </c>
       <c r="B35" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4266,10 +4081,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>435616</v>
+        <v>436090</v>
       </c>
       <c r="R35" t="n">
-        <v>7009098</v>
+        <v>7009214</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4306,7 +4121,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4333,15 +4148,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121291885</v>
+        <v>121291900</v>
       </c>
       <c r="B36" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4373,10 +4183,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>435597</v>
+        <v>436083</v>
       </c>
       <c r="R36" t="n">
-        <v>7009138</v>
+        <v>7009262</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4413,7 +4223,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4440,15 +4250,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121291875</v>
+        <v>121291901</v>
       </c>
       <c r="B37" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4480,10 +4285,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>435652</v>
+        <v>436078</v>
       </c>
       <c r="R37" t="n">
-        <v>7009067</v>
+        <v>7009258</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4547,15 +4352,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121291876</v>
+        <v>121291902</v>
       </c>
       <c r="B38" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4587,10 +4387,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>435652</v>
+        <v>436067</v>
       </c>
       <c r="R38" t="n">
-        <v>7009070</v>
+        <v>7009258</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4627,7 +4427,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4654,15 +4454,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121291854</v>
+        <v>121291903</v>
       </c>
       <c r="B39" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4694,10 +4489,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>435647</v>
+        <v>436023</v>
       </c>
       <c r="R39" t="n">
-        <v>7009072</v>
+        <v>7009315</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4761,10 +4556,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132340980</v>
+        <v>121291904</v>
       </c>
       <c r="B40" t="n">
-        <v>57957</v>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4796,10 +4591,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>435430</v>
+        <v>436021</v>
       </c>
       <c r="R40" t="n">
-        <v>7009465</v>
+        <v>7009316</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4826,17 +4621,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4863,10 +4658,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132340953</v>
+        <v>121291905</v>
       </c>
       <c r="B41" t="n">
-        <v>57957</v>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4898,10 +4693,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>435992</v>
+        <v>435923</v>
       </c>
       <c r="R41" t="n">
-        <v>7009388</v>
+        <v>7009425</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4928,17 +4723,17 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4965,10 +4760,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132340964</v>
+        <v>121291906</v>
       </c>
       <c r="B42" t="n">
-        <v>57957</v>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4994,24 +4789,16 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>435539</v>
+        <v>435791</v>
       </c>
       <c r="R42" t="n">
-        <v>7009104</v>
+        <v>7009510</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5038,17 +4825,17 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Bohål ca 1,7m upp i grantickerötad granhögstubbe</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5075,10 +4862,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132340957</v>
+        <v>121291907</v>
       </c>
       <c r="B43" t="n">
-        <v>57957</v>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5110,10 +4897,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>435678</v>
+        <v>435736</v>
       </c>
       <c r="R43" t="n">
-        <v>7009061</v>
+        <v>7009605</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5140,17 +4927,17 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5177,10 +4964,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132340986</v>
+        <v>121291908</v>
       </c>
       <c r="B44" t="n">
-        <v>57957</v>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5212,10 +4999,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>435632</v>
+        <v>435738</v>
       </c>
       <c r="R44" t="n">
-        <v>7009284</v>
+        <v>7009628</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5242,17 +5029,17 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5279,10 +5066,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132340996</v>
+        <v>121291909</v>
       </c>
       <c r="B45" t="n">
-        <v>57957</v>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5314,10 +5101,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>435657</v>
+        <v>435794</v>
       </c>
       <c r="R45" t="n">
-        <v>7009715</v>
+        <v>7009569</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5344,17 +5131,17 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5381,10 +5168,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132340977</v>
+        <v>121291911</v>
       </c>
       <c r="B46" t="n">
-        <v>57957</v>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5416,10 +5203,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>435438</v>
+        <v>435802</v>
       </c>
       <c r="R46" t="n">
-        <v>7009287</v>
+        <v>7009577</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5446,17 +5233,17 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5483,10 +5270,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132340983</v>
+        <v>132340951</v>
       </c>
       <c r="B47" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5518,10 +5305,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>435570</v>
+        <v>435770</v>
       </c>
       <c r="R47" t="n">
-        <v>7009342</v>
+        <v>7009576</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5585,10 +5372,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132340997</v>
+        <v>132340952</v>
       </c>
       <c r="B48" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5620,10 +5407,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>435714</v>
+        <v>435863</v>
       </c>
       <c r="R48" t="n">
-        <v>7009769</v>
+        <v>7009504</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5660,7 +5447,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5687,10 +5474,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132340974</v>
+        <v>132340953</v>
       </c>
       <c r="B49" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5722,10 +5509,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>435472</v>
+        <v>435992</v>
       </c>
       <c r="R49" t="n">
-        <v>7009247</v>
+        <v>7009388</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5762,7 +5549,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5789,10 +5576,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132340962</v>
+        <v>132340954</v>
       </c>
       <c r="B50" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5824,10 +5611,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>435540</v>
+        <v>435810</v>
       </c>
       <c r="R50" t="n">
-        <v>7009069</v>
+        <v>7009249</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5891,10 +5678,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132340970</v>
+        <v>132340955</v>
       </c>
       <c r="B51" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5926,10 +5713,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>435522</v>
+        <v>435814</v>
       </c>
       <c r="R51" t="n">
-        <v>7009195</v>
+        <v>7009258</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5966,7 +5753,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5993,10 +5780,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132340995</v>
+        <v>132340956</v>
       </c>
       <c r="B52" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6028,10 +5815,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>435651</v>
+        <v>435811</v>
       </c>
       <c r="R52" t="n">
-        <v>7009715</v>
+        <v>7009266</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6068,7 +5855,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6095,10 +5882,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132340971</v>
+        <v>132340957</v>
       </c>
       <c r="B53" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6130,10 +5917,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>435534</v>
+        <v>435678</v>
       </c>
       <c r="R53" t="n">
-        <v>7009201</v>
+        <v>7009061</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6170,7 +5957,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6197,10 +5984,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132340984</v>
+        <v>132340958</v>
       </c>
       <c r="B54" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6232,10 +6019,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>435644</v>
+        <v>435594</v>
       </c>
       <c r="R54" t="n">
-        <v>7009260</v>
+        <v>7009012</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6299,10 +6086,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132340982</v>
+        <v>132340959</v>
       </c>
       <c r="B55" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6334,10 +6121,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>435574</v>
+        <v>435523</v>
       </c>
       <c r="R55" t="n">
-        <v>7009351</v>
+        <v>7009035</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6374,7 +6161,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6401,10 +6188,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132340992</v>
+        <v>132340960</v>
       </c>
       <c r="B56" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6436,10 +6223,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>435652</v>
+        <v>435513</v>
       </c>
       <c r="R56" t="n">
-        <v>7009712</v>
+        <v>7009070</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6476,7 +6263,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6503,10 +6290,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132340989</v>
+        <v>132340961</v>
       </c>
       <c r="B57" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6538,10 +6325,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>435579</v>
+        <v>435531</v>
       </c>
       <c r="R57" t="n">
-        <v>7009462</v>
+        <v>7009066</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6578,7 +6365,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6605,10 +6392,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132340968</v>
+        <v>132340962</v>
       </c>
       <c r="B58" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6640,10 +6427,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>435492</v>
+        <v>435540</v>
       </c>
       <c r="R58" t="n">
-        <v>7009187</v>
+        <v>7009069</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6707,10 +6494,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132340967</v>
+        <v>132340963</v>
       </c>
       <c r="B59" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6742,10 +6529,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>435511</v>
+        <v>435542</v>
       </c>
       <c r="R59" t="n">
-        <v>7009171</v>
+        <v>7009077</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6809,10 +6596,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132340985</v>
+        <v>132340964</v>
       </c>
       <c r="B60" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6852,10 +6639,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>435645</v>
+        <v>435539</v>
       </c>
       <c r="R60" t="n">
-        <v>7009273</v>
+        <v>7009104</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6892,7 +6679,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Bohål ca 1,8 m upp i grantickerötad granhögstubbe.Öppning ca 4,5cm i diameter.Ganska färskt</t>
+          <t>Bohål ca 1,7m upp i grantickerötad granhögstubbe</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6919,10 +6706,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132340988</v>
+        <v>132340965</v>
       </c>
       <c r="B61" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6954,10 +6741,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>435597</v>
+        <v>435503</v>
       </c>
       <c r="R61" t="n">
-        <v>7009455</v>
+        <v>7009162</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7021,10 +6808,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132340965</v>
+        <v>132340966</v>
       </c>
       <c r="B62" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7056,10 +6843,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>435503</v>
+        <v>435505</v>
       </c>
       <c r="R62" t="n">
-        <v>7009162</v>
+        <v>7009166</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7096,7 +6883,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7123,10 +6910,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132340990</v>
+        <v>132340967</v>
       </c>
       <c r="B63" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7158,10 +6945,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>435589</v>
+        <v>435511</v>
       </c>
       <c r="R63" t="n">
-        <v>7009520</v>
+        <v>7009171</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7225,10 +7012,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132340963</v>
+        <v>132340968</v>
       </c>
       <c r="B64" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7260,10 +7047,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>435542</v>
+        <v>435492</v>
       </c>
       <c r="R64" t="n">
-        <v>7009077</v>
+        <v>7009187</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7327,10 +7114,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132340972</v>
+        <v>132340969</v>
       </c>
       <c r="B65" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7362,10 +7149,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>435554</v>
+        <v>435503</v>
       </c>
       <c r="R65" t="n">
-        <v>7009207</v>
+        <v>7009197</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7402,7 +7189,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7429,10 +7216,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132340960</v>
+        <v>132340970</v>
       </c>
       <c r="B66" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7464,10 +7251,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>435513</v>
+        <v>435522</v>
       </c>
       <c r="R66" t="n">
-        <v>7009070</v>
+        <v>7009195</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7531,10 +7318,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132340958</v>
+        <v>132340971</v>
       </c>
       <c r="B67" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7566,10 +7353,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>435594</v>
+        <v>435534</v>
       </c>
       <c r="R67" t="n">
-        <v>7009012</v>
+        <v>7009201</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7606,7 +7393,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7633,10 +7420,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132340975</v>
+        <v>132340972</v>
       </c>
       <c r="B68" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7668,10 +7455,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>435422</v>
+        <v>435554</v>
       </c>
       <c r="R68" t="n">
-        <v>7009269</v>
+        <v>7009207</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7735,10 +7522,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132340955</v>
+        <v>132340973</v>
       </c>
       <c r="B69" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7770,10 +7557,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>435814</v>
+        <v>435536</v>
       </c>
       <c r="R69" t="n">
-        <v>7009258</v>
+        <v>7009212</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7810,7 +7597,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7837,10 +7624,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132340973</v>
+        <v>132340974</v>
       </c>
       <c r="B70" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7872,10 +7659,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>435536</v>
+        <v>435472</v>
       </c>
       <c r="R70" t="n">
-        <v>7009212</v>
+        <v>7009247</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7939,10 +7726,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132340994</v>
+        <v>132340975</v>
       </c>
       <c r="B71" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7974,10 +7761,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>435648</v>
+        <v>435422</v>
       </c>
       <c r="R71" t="n">
-        <v>7009710</v>
+        <v>7009269</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8014,7 +7801,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8041,10 +7828,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132340998</v>
+        <v>132340976</v>
       </c>
       <c r="B72" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8076,10 +7863,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>435702</v>
+        <v>435445</v>
       </c>
       <c r="R72" t="n">
-        <v>7009759</v>
+        <v>7009286</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8116,7 +7903,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8143,10 +7930,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132340966</v>
+        <v>132340977</v>
       </c>
       <c r="B73" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8178,10 +7965,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>435505</v>
+        <v>435438</v>
       </c>
       <c r="R73" t="n">
-        <v>7009166</v>
+        <v>7009287</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8218,7 +8005,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8245,10 +8032,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132340979</v>
+        <v>132340978</v>
       </c>
       <c r="B74" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8280,10 +8067,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>435416</v>
+        <v>435358</v>
       </c>
       <c r="R74" t="n">
-        <v>7009430</v>
+        <v>7009404</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8320,7 +8107,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8347,10 +8134,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132340956</v>
+        <v>132340979</v>
       </c>
       <c r="B75" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8382,10 +8169,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>435811</v>
+        <v>435416</v>
       </c>
       <c r="R75" t="n">
-        <v>7009266</v>
+        <v>7009430</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8449,10 +8236,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132340954</v>
+        <v>132340980</v>
       </c>
       <c r="B76" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8484,10 +8271,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>435810</v>
+        <v>435430</v>
       </c>
       <c r="R76" t="n">
-        <v>7009249</v>
+        <v>7009465</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8551,10 +8338,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132341121</v>
+        <v>132340981</v>
       </c>
       <c r="B77" t="n">
-        <v>91912</v>
+        <v>57975</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8562,21 +8349,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8586,10 +8373,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>435520</v>
+        <v>435542</v>
       </c>
       <c r="R77" t="n">
-        <v>7009134</v>
+        <v>7009456</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8622,6 +8409,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8648,10 +8440,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132340952</v>
+        <v>132340982</v>
       </c>
       <c r="B78" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8683,10 +8475,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>435863</v>
+        <v>435574</v>
       </c>
       <c r="R78" t="n">
-        <v>7009504</v>
+        <v>7009351</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8750,10 +8542,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132340976</v>
+        <v>132340983</v>
       </c>
       <c r="B79" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8785,10 +8577,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>435445</v>
+        <v>435570</v>
       </c>
       <c r="R79" t="n">
-        <v>7009286</v>
+        <v>7009342</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8825,7 +8617,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8852,10 +8644,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132340961</v>
+        <v>132340984</v>
       </c>
       <c r="B80" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8887,10 +8679,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>435531</v>
+        <v>435644</v>
       </c>
       <c r="R80" t="n">
-        <v>7009066</v>
+        <v>7009260</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8927,7 +8719,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8954,10 +8746,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132340987</v>
+        <v>132340985</v>
       </c>
       <c r="B81" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8983,16 +8775,24 @@
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>435703</v>
+        <v>435645</v>
       </c>
       <c r="R81" t="n">
-        <v>7009319</v>
+        <v>7009273</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9029,7 +8829,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Bohål ca 1,8 m upp i grantickerötad granhögstubbe.Öppning ca 4,5cm i diameter.Ganska färskt</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9056,10 +8856,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132340991</v>
+        <v>132340986</v>
       </c>
       <c r="B82" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9091,10 +8891,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>435608</v>
+        <v>435632</v>
       </c>
       <c r="R82" t="n">
-        <v>7009554</v>
+        <v>7009284</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9131,7 +8931,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9158,10 +8958,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132341120</v>
+        <v>132340987</v>
       </c>
       <c r="B83" t="n">
-        <v>91912</v>
+        <v>57975</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9169,21 +8969,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9193,10 +8993,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>435875</v>
+        <v>435703</v>
       </c>
       <c r="R83" t="n">
-        <v>7009285</v>
+        <v>7009319</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9229,6 +9029,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9255,10 +9060,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132340978</v>
+        <v>132340988</v>
       </c>
       <c r="B84" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9290,10 +9095,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>435358</v>
+        <v>435597</v>
       </c>
       <c r="R84" t="n">
-        <v>7009404</v>
+        <v>7009455</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9357,10 +9162,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132340951</v>
+        <v>132340989</v>
       </c>
       <c r="B85" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9392,10 +9197,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>435770</v>
+        <v>435579</v>
       </c>
       <c r="R85" t="n">
-        <v>7009576</v>
+        <v>7009462</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9459,10 +9264,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132340969</v>
+        <v>132340990</v>
       </c>
       <c r="B86" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9494,10 +9299,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>435503</v>
+        <v>435589</v>
       </c>
       <c r="R86" t="n">
-        <v>7009197</v>
+        <v>7009520</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9534,7 +9339,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9561,10 +9366,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132340959</v>
+        <v>132340991</v>
       </c>
       <c r="B87" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9596,10 +9401,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>435523</v>
+        <v>435608</v>
       </c>
       <c r="R87" t="n">
-        <v>7009035</v>
+        <v>7009554</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9663,7 +9468,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>133454007</v>
+        <v>132340992</v>
       </c>
       <c r="B88" t="n">
         <v>57975</v>
@@ -9698,10 +9503,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>435565</v>
+        <v>435652</v>
       </c>
       <c r="R88" t="n">
-        <v>7008890</v>
+        <v>7009712</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9728,17 +9533,17 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9765,7 +9570,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>133454010</v>
+        <v>132340994</v>
       </c>
       <c r="B89" t="n">
         <v>57975</v>
@@ -9800,10 +9605,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>435604</v>
+        <v>435648</v>
       </c>
       <c r="R89" t="n">
-        <v>7008900</v>
+        <v>7009710</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9830,17 +9635,17 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9867,7 +9672,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>133454009</v>
+        <v>132340995</v>
       </c>
       <c r="B90" t="n">
         <v>57975</v>
@@ -9902,10 +9707,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>435569</v>
+        <v>435651</v>
       </c>
       <c r="R90" t="n">
-        <v>7008908</v>
+        <v>7009715</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9932,17 +9737,17 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9969,10 +9774,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>133454055</v>
+        <v>132340996</v>
       </c>
       <c r="B91" t="n">
-        <v>91955</v>
+        <v>57975</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9980,21 +9785,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10004,10 +9809,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>435564</v>
+        <v>435657</v>
       </c>
       <c r="R91" t="n">
-        <v>7008805</v>
+        <v>7009715</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10034,12 +9839,17 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10063,6 +9873,516 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>132340997</v>
+      </c>
+      <c r="B92" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Sällsjön Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>435714</v>
+      </c>
+      <c r="R92" t="n">
+        <v>7009769</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>132340998</v>
+      </c>
+      <c r="B93" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Sällsjön Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>435702</v>
+      </c>
+      <c r="R93" t="n">
+        <v>7009759</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>133454007</v>
+      </c>
+      <c r="B94" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Sällsjön Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>435565</v>
+      </c>
+      <c r="R94" t="n">
+        <v>7008890</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>133454009</v>
+      </c>
+      <c r="B95" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Sällsjön Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>435569</v>
+      </c>
+      <c r="R95" t="n">
+        <v>7008908</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>133454010</v>
+      </c>
+      <c r="B96" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Sällsjön Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>435604</v>
+      </c>
+      <c r="R96" t="n">
+        <v>7008900</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11380-2026 artfynd.xlsx
+++ b/artfynd/A 11380-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY96"/>
+  <dimension ref="A1:AZ96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341120</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341121</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133454055</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121291854</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1167,6 +1192,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121291869</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1269,6 +1299,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121291870</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1371,6 +1406,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121291871</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1473,6 +1513,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121291872</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1575,6 +1620,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121291873</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1677,6 +1727,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121291874</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1779,6 +1834,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121291875</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1881,6 +1941,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121291876</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1983,6 +2048,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121291877</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2085,6 +2155,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121291878</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2187,6 +2262,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121291879</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2289,6 +2369,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121291880</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2391,6 +2476,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121291881</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2493,6 +2583,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121291882</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2595,6 +2690,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121291883</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2697,6 +2797,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121291884</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2799,6 +2904,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121291885</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2921,6 +3031,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121291886</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3023,6 +3138,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121291887</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3125,6 +3245,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121291888</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3227,6 +3352,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121291889</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3329,6 +3459,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121291890</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3431,6 +3566,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121291891</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3533,6 +3673,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121291892</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3635,6 +3780,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121291893</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3737,6 +3887,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121291894</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3839,6 +3994,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121291896</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3941,6 +4101,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121291897</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4043,6 +4208,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121291898</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4145,6 +4315,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121291899</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4247,6 +4422,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121291900</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4349,6 +4529,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121291901</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4451,6 +4636,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121291902</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4553,6 +4743,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121291903</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4655,6 +4850,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121291904</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4757,6 +4957,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121291905</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4859,6 +5064,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121291906</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4961,6 +5171,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121291907</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5063,6 +5278,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121291908</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5165,6 +5385,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121291909</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5267,6 +5492,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121291911</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5369,6 +5599,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340951</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5471,6 +5706,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340952</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5573,6 +5813,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340953</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5675,6 +5920,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340954</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5777,6 +6027,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340955</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5879,6 +6134,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340956</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5981,6 +6241,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340957</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6083,6 +6348,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340958</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6185,6 +6455,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340959</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6287,6 +6562,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340960</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6389,6 +6669,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340961</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6491,6 +6776,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340962</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6593,6 +6883,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340963</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6703,6 +6998,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340964</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6805,6 +7105,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340965</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6907,6 +7212,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340966</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7009,6 +7319,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340967</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7111,6 +7426,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340968</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7213,6 +7533,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340969</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7315,6 +7640,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340970</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7417,6 +7747,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340971</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7519,6 +7854,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340972</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7621,6 +7961,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340973</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7723,6 +8068,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340974</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7825,6 +8175,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340975</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7927,6 +8282,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340976</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8029,6 +8389,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340977</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8131,6 +8496,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340978</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8233,6 +8603,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340979</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8335,6 +8710,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340980</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8437,6 +8817,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340981</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8539,6 +8924,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340982</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8641,6 +9031,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340983</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8743,6 +9138,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340984</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8853,6 +9253,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340985</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8955,6 +9360,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340986</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9057,6 +9467,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340987</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9159,6 +9574,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340988</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9261,6 +9681,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340989</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9363,6 +9788,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340990</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9465,6 +9895,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340991</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9567,6 +10002,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340992</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9669,6 +10109,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340994</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9771,6 +10216,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340995</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9873,6 +10323,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340996</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9975,6 +10430,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340997</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10077,6 +10537,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340998</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10179,6 +10644,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133454007</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10281,6 +10751,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133454009</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10383,8 +10858,110 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133454010</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>